--- a/excel/sample.xlsx
+++ b/excel/sample.xlsx
@@ -2,25 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skillfort\SkillFortClass\DataAnalytics03\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F4284E-3132-4654-AA63-37F4946DFB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C2568C-3150-4582-9535-C895F355E4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="link" sheetId="4" r:id="rId4"/>
-    <sheet name="text" sheetId="5" r:id="rId5"/>
+    <sheet name="rawdata" sheetId="1" r:id="rId1"/>
+    <sheet name="lookup" sheetId="3" r:id="rId2"/>
+    <sheet name="index and match" sheetId="7" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="10" r:id="rId4"/>
+    <sheet name="Pivot" sheetId="8" r:id="rId5"/>
+    <sheet name="filter" sheetId="2" r:id="rId6"/>
+    <sheet name="link" sheetId="4" r:id="rId7"/>
+    <sheet name="text" sheetId="5" r:id="rId8"/>
+    <sheet name="datetime" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rawdata!$A$1:$G$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="557">
   <si>
     <t>ID</t>
   </si>
@@ -844,202 +848,1025 @@
     <t>name</t>
   </si>
   <si>
-    <t>product_name</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>gst</t>
+    <t>Linkedin</t>
+  </si>
+  <si>
+    <t>Monisha</t>
+  </si>
+  <si>
+    <t>mobile</t>
+  </si>
+  <si>
+    <t>+91-8989889989</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>2024E001</t>
+  </si>
+  <si>
+    <t>2024SS0001</t>
+  </si>
+  <si>
+    <t>EmployeeCode</t>
+  </si>
+  <si>
+    <t>text before</t>
+  </si>
+  <si>
+    <t>textAfter</t>
+  </si>
+  <si>
+    <t>Sundar Lingam</t>
+  </si>
+  <si>
+    <t>options</t>
+  </si>
+  <si>
+    <t>Sundar Lingam Chennai</t>
+  </si>
+  <si>
+    <t>use instance number</t>
+  </si>
+  <si>
+    <t>match end if not found</t>
+  </si>
+  <si>
+    <t>if not found</t>
+  </si>
+  <si>
+    <t>Data science,python,django</t>
+  </si>
+  <si>
+    <t>Data science</t>
+  </si>
+  <si>
+    <t>split text into Columns</t>
+  </si>
+  <si>
+    <t>column and row</t>
+  </si>
+  <si>
+    <t>ignore or Keep Empty Value</t>
+  </si>
+  <si>
+    <t>Data science,,python,django</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Find</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>find the Position of given text/char withiin the content</t>
+  </si>
+  <si>
+    <t>ignores case sensitive and find the position</t>
+  </si>
+  <si>
+    <t>size of the given text content</t>
+  </si>
+  <si>
+    <t>Example:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find </t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>the quick brown fox jumped over the lazy dog</t>
+  </si>
+  <si>
+    <t>The quick brown fox jumped over the lazy dog</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>Concatenate</t>
+  </si>
+  <si>
+    <t>text join</t>
+  </si>
+  <si>
+    <t>(&amp;)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Joining text values from cells or strings</t>
+  </si>
+  <si>
+    <t>joining text calues but also support range of cells</t>
+  </si>
+  <si>
+    <t>joining text values with additional suports of delimiter</t>
+  </si>
+  <si>
+    <t>directly</t>
+  </si>
+  <si>
+    <t>Sundar</t>
+  </si>
+  <si>
+    <t>Lingam</t>
+  </si>
+  <si>
+    <t>MID(A10,5,1)</t>
+  </si>
+  <si>
+    <t>RIGHT(A2,10)</t>
+  </si>
+  <si>
+    <t>LEFT(A2,3)</t>
+  </si>
+  <si>
+    <t>Data science,python,django|SQL ,postgress|pandas,seaborn</t>
+  </si>
+  <si>
+    <t>concat(Range select panrapa space add pana mudiyathu)</t>
+  </si>
+  <si>
+    <t>Helo</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>Sundhar</t>
+  </si>
+  <si>
+    <t>Also</t>
+  </si>
+  <si>
+    <t xml:space="preserve">called </t>
+  </si>
+  <si>
+    <t>sundar</t>
+  </si>
+  <si>
+    <t>TEXTJOIN(" ",TRUE,A57:A65)</t>
+  </si>
+  <si>
+    <t>A57&amp;A58&amp;A59</t>
+  </si>
+  <si>
+    <t>CONCAT(D49:F49)</t>
+  </si>
+  <si>
+    <t>CONCATENATE(D48," ",E48,F48,B48)</t>
+  </si>
+  <si>
+    <t>CONCAT(D49," ",E49)</t>
+  </si>
+  <si>
+    <t>Upper</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>proper</t>
+  </si>
+  <si>
+    <t>Believe you can and you are halfway there</t>
+  </si>
+  <si>
+    <t>They Key to Success is to focus to the GOAL you want to achieve in you Life, not the Obstacles</t>
+  </si>
+  <si>
+    <t>Focus on the GOAL</t>
+  </si>
+  <si>
+    <t>upper()</t>
+  </si>
+  <si>
+    <t>lower()</t>
+  </si>
+  <si>
+    <t>proper()</t>
+  </si>
+  <si>
+    <t>Replace and Substitute</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
+    <t>substitute</t>
+  </si>
+  <si>
+    <t>Replace part of the text based on its Position</t>
+  </si>
+  <si>
+    <t>bsed on Matching Text</t>
+  </si>
+  <si>
+    <t>REPLACE(C72,9,3,"u")</t>
+  </si>
+  <si>
+    <t>SUBSTITUTE(C72,"you","u",1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>php,java,php</t>
+  </si>
+  <si>
+    <t>2 occurance matum change pananum</t>
+  </si>
+  <si>
+    <t>Date time</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>today</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>Creates a valid date from separate year,month and days</t>
+  </si>
+  <si>
+    <t>Creates a time value from parts</t>
+  </si>
+  <si>
+    <t>combine date + time to create Date time</t>
+  </si>
+  <si>
+    <t>return the current system date</t>
+  </si>
+  <si>
+    <t>current date and time</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Rallway time</t>
+  </si>
+  <si>
+    <t>TIME(21,20,10)</t>
+  </si>
+  <si>
+    <t>DATE(2026,9,1)+TIME(1,45,34)</t>
+  </si>
+  <si>
+    <t>change format with custom</t>
+  </si>
+  <si>
+    <t>DATE(year,month,day)</t>
+  </si>
+  <si>
+    <t>TIME(hr,min,sec)</t>
+  </si>
+  <si>
+    <t>today()</t>
+  </si>
+  <si>
+    <t>now()</t>
+  </si>
+  <si>
+    <t>Date time conversion</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">date </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text to date</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">time </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text to date</t>
+    </r>
+  </si>
+  <si>
+    <t>extract</t>
+  </si>
+  <si>
+    <t>day(serial_number)</t>
+  </si>
+  <si>
+    <t>month(serial_number)</t>
+  </si>
+  <si>
+    <t>year(serial_number)</t>
+  </si>
+  <si>
+    <t>hour(serial_number)</t>
+  </si>
+  <si>
+    <t>minute(serial_number)</t>
+  </si>
+  <si>
+    <t>seconds(serial_number)</t>
+  </si>
+  <si>
+    <t>weeknum(serial_number,return_type)</t>
+  </si>
+  <si>
+    <t>weekday(serial_number,return_type)</t>
+  </si>
+  <si>
+    <t>Date Difference</t>
+  </si>
+  <si>
+    <t>Date Dif</t>
+  </si>
+  <si>
+    <t>in years</t>
+  </si>
+  <si>
+    <t>in months</t>
+  </si>
+  <si>
+    <t>in days</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>no of days between 2 dates</t>
+  </si>
+  <si>
+    <t>net work days</t>
+  </si>
+  <si>
+    <t>working days between two dates</t>
+  </si>
+  <si>
+    <t>include holiday</t>
+  </si>
+  <si>
+    <t>network days,intl</t>
+  </si>
+  <si>
+    <t>year fraction</t>
+  </si>
+  <si>
+    <t>Optionally configuring weekends</t>
+  </si>
+  <si>
+    <t>calculate fractional year between 2 dates</t>
+  </si>
+  <si>
+    <t>datedif(date1,date2,"Y")</t>
+  </si>
+  <si>
+    <t>datedif(date1,date2,"m")</t>
+  </si>
+  <si>
+    <t>datedif(date1,date2,"d")</t>
+  </si>
+  <si>
+    <t>days(end_date,start_date)</t>
+  </si>
+  <si>
+    <t>NETWORKDAYS(start_date,end_date,holiday list)</t>
+  </si>
+  <si>
+    <t>NETWORKDAYS(C27,D27)</t>
+  </si>
+  <si>
+    <t>Date addition/adjustments</t>
+  </si>
+  <si>
+    <t>edate</t>
+  </si>
+  <si>
+    <t>EOMONTH(C33,3)</t>
+  </si>
+  <si>
+    <t>EDATE(C33,3)</t>
+  </si>
+  <si>
+    <t>WORKDAY(C33,5)</t>
+  </si>
+  <si>
+    <t>Lookup</t>
+  </si>
+  <si>
+    <t>V lookup</t>
+  </si>
+  <si>
+    <t>H lookup</t>
+  </si>
+  <si>
+    <t>lookup</t>
+  </si>
+  <si>
+    <t>X lookup</t>
+  </si>
+  <si>
+    <t>New -both V and H</t>
+  </si>
+  <si>
+    <t>old version - need sorting before</t>
+  </si>
+  <si>
+    <t>Row wise</t>
+  </si>
+  <si>
+    <t>Column wise</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>VLOOKUP(A8,rawdata!A$2:G$101,7,0)</t>
+  </si>
+  <si>
+    <t>Vlookup</t>
+  </si>
+  <si>
+    <t>xlookup</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>22S0280</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>match</t>
+  </si>
+  <si>
+    <t>X match</t>
+  </si>
+  <si>
+    <t>Get Value based on cell Location</t>
+  </si>
+  <si>
+    <t>Get cell location based on Value</t>
+  </si>
+  <si>
+    <t>Additional Configuration with Match</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>row</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>MATCH("f",G6:G8,0)</t>
+  </si>
+  <si>
+    <t>MATCH("f",E7:I7,0)</t>
+  </si>
+  <si>
+    <t>xmatch</t>
+  </si>
+  <si>
+    <t>XMATCH("d",E7:I7,0,-1)</t>
+  </si>
+  <si>
+    <t>INDEX(E6:E8,1,1)</t>
+  </si>
+  <si>
+    <t>INDEX(E6:I6,1,3)</t>
+  </si>
+  <si>
+    <t>INDEX(E6:I8,3,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">course </t>
+  </si>
+  <si>
+    <t>registration</t>
+  </si>
+  <si>
+    <t>EG:</t>
+  </si>
+  <si>
+    <t>Data Analytics</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>Choose Course</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Manoj</t>
+  </si>
+  <si>
+    <t>MATCH(F18,A17:A20,0)</t>
+  </si>
+  <si>
+    <t>we can choose only row or column</t>
+  </si>
+  <si>
+    <t>Order_ID</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Salesperson</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit_Price</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Payment_Mode</t>
+  </si>
+  <si>
+    <t>ORD001</t>
+  </si>
+  <si>
+    <t>Arun</t>
+  </si>
+  <si>
+    <t>North</t>
   </si>
   <si>
     <t>Laptop</t>
   </si>
   <si>
-    <t>tv</t>
-  </si>
-  <si>
-    <t>fridege</t>
-  </si>
-  <si>
-    <t>Linkedin</t>
-  </si>
-  <si>
-    <t>Monisha</t>
-  </si>
-  <si>
-    <t>mobile</t>
-  </si>
-  <si>
-    <t>+91-8989889989</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>2024E001</t>
-  </si>
-  <si>
-    <t>2024SS0001</t>
-  </si>
-  <si>
-    <t>EmployeeCode</t>
-  </si>
-  <si>
-    <t>text before</t>
-  </si>
-  <si>
-    <t>textAfter</t>
-  </si>
-  <si>
-    <t>Sundar Lingam</t>
-  </si>
-  <si>
-    <t>options</t>
-  </si>
-  <si>
-    <t>Sundar Lingam Chennai</t>
-  </si>
-  <si>
-    <t>use instance number</t>
-  </si>
-  <si>
-    <t>match end if not found</t>
-  </si>
-  <si>
-    <t>if not found</t>
-  </si>
-  <si>
-    <t>Data science,python,django</t>
-  </si>
-  <si>
-    <t>Data science</t>
-  </si>
-  <si>
-    <t>split text into Columns</t>
-  </si>
-  <si>
-    <t>column and row</t>
-  </si>
-  <si>
-    <t>ignore or Keep Empty Value</t>
-  </si>
-  <si>
-    <t>Data science,,python,django</t>
-  </si>
-  <si>
-    <t>Search</t>
-  </si>
-  <si>
-    <t>Find</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>find the Position of given text/char withiin the content</t>
-  </si>
-  <si>
-    <t>ignores case sensitive and find the position</t>
-  </si>
-  <si>
-    <t>size of the given text content</t>
-  </si>
-  <si>
-    <t>Example:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find </t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>Length</t>
-  </si>
-  <si>
-    <t>brown</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>the quick brown fox jumped over the lazy dog</t>
-  </si>
-  <si>
-    <t>The quick brown fox jumped over the lazy dog</t>
-  </si>
-  <si>
-    <t>the</t>
-  </si>
-  <si>
-    <t>Concatenate</t>
-  </si>
-  <si>
-    <t>concat</t>
-  </si>
-  <si>
-    <t>text join</t>
-  </si>
-  <si>
-    <t>(&amp;)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Joining text values from cells or strings</t>
-  </si>
-  <si>
-    <t>joining text calues but also support range of cells</t>
-  </si>
-  <si>
-    <t>joining text values with additional suports of delimiter</t>
-  </si>
-  <si>
-    <t>directly</t>
-  </si>
-  <si>
-    <t>Sundar</t>
-  </si>
-  <si>
-    <t>Lingam</t>
-  </si>
-  <si>
-    <t>MID(A10,5,1)</t>
-  </si>
-  <si>
-    <t>RIGHT(A2,10)</t>
-  </si>
-  <si>
-    <t>LEFT(A2,3)</t>
-  </si>
-  <si>
-    <t>Data science,python,django|SQL ,postgress|pandas,seaborn</t>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>ORD002</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>UPI</t>
+  </si>
+  <si>
+    <t>ORD003</t>
+  </si>
+  <si>
+    <t>Karthik</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>ORD004</t>
+  </si>
+  <si>
+    <t>Divya</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>ORD005</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>ORD006</t>
+  </si>
+  <si>
+    <t>Headset</t>
+  </si>
+  <si>
+    <t>ORD007</t>
+  </si>
+  <si>
+    <t>ORD008</t>
+  </si>
+  <si>
+    <t>ORD009</t>
+  </si>
+  <si>
+    <t>ORD010</t>
+  </si>
+  <si>
+    <t>ORD011</t>
+  </si>
+  <si>
+    <t>ORD012</t>
+  </si>
+  <si>
+    <t>ORD013</t>
+  </si>
+  <si>
+    <t>ORD014</t>
+  </si>
+  <si>
+    <t>ORD015</t>
+  </si>
+  <si>
+    <t>ORD016</t>
+  </si>
+  <si>
+    <t>ORD017</t>
+  </si>
+  <si>
+    <t>ORD018</t>
+  </si>
+  <si>
+    <t>ORD019</t>
+  </si>
+  <si>
+    <t>ORD020</t>
+  </si>
+  <si>
+    <t>ORD021</t>
+  </si>
+  <si>
+    <t>ORD022</t>
+  </si>
+  <si>
+    <t>ORD023</t>
+  </si>
+  <si>
+    <t>ORD024</t>
+  </si>
+  <si>
+    <t>ORD025</t>
+  </si>
+  <si>
+    <t>ORD026</t>
+  </si>
+  <si>
+    <t>ORD027</t>
+  </si>
+  <si>
+    <t>ORD028</t>
+  </si>
+  <si>
+    <t>ORD029</t>
+  </si>
+  <si>
+    <t>ORD030</t>
+  </si>
+  <si>
+    <t>ORD031</t>
+  </si>
+  <si>
+    <t>ORD032</t>
+  </si>
+  <si>
+    <t>ORD033</t>
+  </si>
+  <si>
+    <t>ORD034</t>
+  </si>
+  <si>
+    <t>ORD035</t>
+  </si>
+  <si>
+    <t>ORD036</t>
+  </si>
+  <si>
+    <t>ORD037</t>
+  </si>
+  <si>
+    <t>ORD038</t>
+  </si>
+  <si>
+    <t>ORD039</t>
+  </si>
+  <si>
+    <t>ORD040</t>
+  </si>
+  <si>
+    <t>ORD041</t>
+  </si>
+  <si>
+    <t>ORD042</t>
+  </si>
+  <si>
+    <t>ORD043</t>
+  </si>
+  <si>
+    <t>ORD044</t>
+  </si>
+  <si>
+    <t>ORD045</t>
+  </si>
+  <si>
+    <t>ORD046</t>
+  </si>
+  <si>
+    <t>ORD047</t>
+  </si>
+  <si>
+    <t>ORD048</t>
+  </si>
+  <si>
+    <t>ORD049</t>
+  </si>
+  <si>
+    <t>ORD050</t>
+  </si>
+  <si>
+    <t>Region-wise total Revenue</t>
+  </si>
+  <si>
+    <t>Salesperson-wise total Revenue</t>
+  </si>
+  <si>
+    <t>Product-wise total Quantity sold</t>
+  </si>
+  <si>
+    <t>Product-wise total Revenue</t>
+  </si>
+  <si>
+    <t>Category-wise Revenue</t>
+  </si>
+  <si>
+    <t>Region-wise Average Revenue</t>
+  </si>
+  <si>
+    <t>Payment Mode-wise total Revenue</t>
+  </si>
+  <si>
+    <t>Salesperson + Region → Total Revenue</t>
+  </si>
+  <si>
+    <t>Region + Product → Total Quantity</t>
+  </si>
+  <si>
+    <t>Salesperson + Product → Total Revenue</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Find </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>which product generated the highest Revenue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Find </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>which Region generated the highest Revenue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Find </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>which Salesperson handled the highest number of Orders</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Show </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Region in Rows, Product in Columns, Revenue in Values</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Show </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Salesperson in Rows, Payment Mode in Columns, Revenue in Values</t>
+    </r>
+  </si>
+  <si>
+    <t>DATEVALUE(C10)</t>
+  </si>
+  <si>
+    <t>date2</t>
+  </si>
+  <si>
+    <t>Date1</t>
+  </si>
+  <si>
+    <t>without lock</t>
+  </si>
+  <si>
+    <t>withlock</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1071,8 +1898,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1133,8 +1974,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1142,71 +2001,211 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="18" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="18" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1512,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1522,7 +2521,7 @@
     <col min="7" max="7" width="12.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14">
+    <row r="1" spans="1:17" ht="14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +2544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14">
+    <row r="2" spans="1:17" ht="14">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1568,7 +2567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14">
+    <row r="3" spans="1:17" ht="14">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -1612,8 +2611,12 @@
       <c r="O3" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="14">
+      <c r="Q3">
+        <f>DAY(D2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="14">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -1656,8 +2659,12 @@
       <c r="O4" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="14">
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q13" si="0">DAY(D3)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="14">
       <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
@@ -1700,8 +2707,12 @@
       <c r="O5" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="14">
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="14">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
@@ -1744,8 +2755,12 @@
       <c r="O6" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="14">
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="14">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1788,8 +2803,12 @@
       <c r="O7" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="14">
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="14">
       <c r="A8" s="9" t="s">
         <v>28</v>
       </c>
@@ -1832,8 +2851,12 @@
       <c r="O8" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="14">
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="14">
       <c r="A9" s="9" t="s">
         <v>31</v>
       </c>
@@ -1876,8 +2899,12 @@
       <c r="O9" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="14">
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="14">
       <c r="A10" s="7" t="s">
         <v>34</v>
       </c>
@@ -1920,8 +2947,12 @@
       <c r="O10" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="14">
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="14">
       <c r="A11" s="11" t="s">
         <v>37</v>
       </c>
@@ -1964,8 +2995,12 @@
       <c r="O11" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="14">
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="14">
       <c r="A12" s="9" t="s">
         <v>40</v>
       </c>
@@ -2008,8 +3043,12 @@
       <c r="O12" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="14">
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="14">
       <c r="A13" s="9" t="s">
         <v>42</v>
       </c>
@@ -2052,8 +3091,12 @@
       <c r="O13" t="str">
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="14">
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="14">
       <c r="A14" s="9" t="s">
         <v>45</v>
       </c>
@@ -2097,7 +3140,7 @@
         <v>Panruti</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14">
+    <row r="15" spans="1:17" ht="14">
       <c r="A15" s="7" t="s">
         <v>48</v>
       </c>
@@ -2141,7 +3184,7 @@
         <v>Panruti</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14">
+    <row r="16" spans="1:17" ht="14">
       <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
@@ -4758,78 +5801,2630 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F700E6B1-D1A5-4261-AFA3-01D0C2A0EAD0}">
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" customWidth="1"/>
+    <col min="8" max="8" width="12.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" ht="15">
+      <c r="A1" s="37" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15">
+      <c r="A2" s="36" t="s">
+        <v>406</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="D2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15">
+      <c r="A3" s="36" t="s">
+        <v>407</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
+      <c r="A4" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" s="36"/>
+      <c r="B6" s="37"/>
+    </row>
+    <row r="7" spans="1:5" ht="15">
+      <c r="A7" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="37"/>
+    </row>
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="77" t="s">
+        <v>556</v>
+      </c>
+      <c r="E8" s="77" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="str">
+        <f>VLOOKUP(A9,rawdata!A:B,2,0)</f>
+        <v>Zohaann</v>
+      </c>
+      <c r="C9" t="str">
+        <f>VLOOKUP(A9,rawdata!A$2:G$101,7,0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="D9">
+        <f>VLOOKUP(A9,rawdata!$A$2:$G$101,3,0)</f>
+        <v>19</v>
+      </c>
+      <c r="E9" t="str">
+        <f>VLOOKUP(A9,rawdata!A2:B101,2,0)</f>
+        <v>Zohaann</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="str">
+        <f>VLOOKUP(A10,rawdata!A:B,2,0)</f>
+        <v>Aditya</v>
+      </c>
+      <c r="C10" t="str">
+        <f>VLOOKUP(A10,rawdata!A$2:G$101,7,0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="D10">
+        <f>VLOOKUP(A10,rawdata!$A$2:$G$101,3,0)</f>
+        <v>18</v>
+      </c>
+      <c r="E10" t="str">
+        <f>VLOOKUP(A10,rawdata!A3:B102,2,0)</f>
+        <v>Aditya</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="str">
+        <f>VLOOKUP(A11,rawdata!A:B,2,0)</f>
+        <v>Rudra</v>
+      </c>
+      <c r="C11" t="str">
+        <f>VLOOKUP(A11,rawdata!A$2:G$101,7,0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="D11">
+        <f>VLOOKUP(A11,rawdata!$A$2:$G$101,3,0)</f>
+        <v>26</v>
+      </c>
+      <c r="E11" t="str">
+        <f>VLOOKUP(A11,rawdata!A4:B103,2,0)</f>
+        <v>Rudra</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="str">
+        <f>VLOOKUP(A12,rawdata!A:B,2,0)</f>
+        <v>Shlok</v>
+      </c>
+      <c r="C12" t="str">
+        <f>VLOOKUP(A12,rawdata!A$2:G$101,7,0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="D12">
+        <f>VLOOKUP(A12,rawdata!$A$2:$G$101,3,0)</f>
+        <v>25</v>
+      </c>
+      <c r="E12" t="str">
+        <f>VLOOKUP(A12,rawdata!A5:B104,2,0)</f>
+        <v>Shlok</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="str">
+        <f>VLOOKUP(A13,rawdata!A:B,2,0)</f>
+        <v>Arjun</v>
+      </c>
+      <c r="C13" t="str">
+        <f>VLOOKUP(A13,rawdata!A$2:G$101,7,0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="D13">
+        <f>VLOOKUP(A13,rawdata!$A$2:$G$101,3,0)</f>
+        <v>16</v>
+      </c>
+      <c r="E13" t="str">
+        <f>VLOOKUP(A13,rawdata!A6:B105,2,0)</f>
+        <v>Arjun</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="str">
+        <f>VLOOKUP(A14,rawdata!A:B,2,0)</f>
+        <v>Mokshn</v>
+      </c>
+      <c r="C14" t="str">
+        <f>VLOOKUP(A14,rawdata!A$2:G$101,7,0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="D14">
+        <f>VLOOKUP(A14,rawdata!$A$2:$G$101,3,0)</f>
+        <v>19</v>
+      </c>
+      <c r="E14" t="str">
+        <f>VLOOKUP(A14,rawdata!A7:B106,2,0)</f>
+        <v>Mokshn</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <f>VLOOKUP(A15,rawdata!$A$2:$G$101,3,0)</f>
+        <v>17</v>
+      </c>
+      <c r="E15" t="e">
+        <f>VLOOKUP(A15,rawdata!A8:B107,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15">
+      <c r="A16" s="36" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15">
+      <c r="A17" s="36" t="str" cm="1">
+        <f t="array" ref="A17:H23">TRANSPOSE(rawdata!A1:G8)</f>
+        <v>ID</v>
+      </c>
+      <c r="B17" t="str">
+        <v>22S001</v>
+      </c>
+      <c r="C17" t="str">
+        <v>22S002</v>
+      </c>
+      <c r="D17" t="str">
+        <v>22S003</v>
+      </c>
+      <c r="E17" t="str">
+        <v>22S004</v>
+      </c>
+      <c r="F17" t="str">
+        <v>22S005</v>
+      </c>
+      <c r="G17" t="str">
+        <v>22S006</v>
+      </c>
+      <c r="H17" t="str">
+        <v>22S007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15">
+      <c r="A18" s="36" t="str">
+        <v>NAME</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Rian</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Shreshthn</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Aymann</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Zohaann</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Lakshann</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Pranitn</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Madhavn</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15">
+      <c r="A19" s="36" t="str">
+        <v>AGE</v>
+      </c>
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>21</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+      <c r="E19">
+        <v>19</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
+      </c>
+      <c r="G19">
+        <v>27</v>
+      </c>
+      <c r="H19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15">
+      <c r="A20" s="36" t="str">
+        <v>JOINED</v>
+      </c>
+      <c r="B20">
+        <v>44563</v>
+      </c>
+      <c r="C20">
+        <v>44570</v>
+      </c>
+      <c r="D20">
+        <v>44576</v>
+      </c>
+      <c r="E20">
+        <v>44577</v>
+      </c>
+      <c r="F20">
+        <v>44578</v>
+      </c>
+      <c r="G20">
+        <v>44578</v>
+      </c>
+      <c r="H20">
+        <v>44585</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15">
+      <c r="A21" s="36" t="str">
+        <v>COMPLETED</v>
+      </c>
+      <c r="B21">
+        <v>44593</v>
+      </c>
+      <c r="C21">
+        <v>44612</v>
+      </c>
+      <c r="D21">
+        <v>44628</v>
+      </c>
+      <c r="E21">
+        <v>44613</v>
+      </c>
+      <c r="F21">
+        <v>44612</v>
+      </c>
+      <c r="G21">
+        <v>44629</v>
+      </c>
+      <c r="H21">
+        <v>44639</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15">
+      <c r="A22" s="36" t="str">
+        <v>AREA</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Beach Road</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Keeranathan</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Ratchagar Nager</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Beach Road</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Vanniyar Palayam</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Keeranathan</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Varakalpattu</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15">
+      <c r="A23" s="36" t="str">
+        <v>CITY</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Chidambaram</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Chidambaram</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Pondicherry</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Panruti</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Cuddalore</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Neyveli</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Cuddalore</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15">
+      <c r="A25" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>414</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="str">
+        <f>HLOOKUP(A26,_xlfn.ANCHORARRAY(A$17),2,0)</f>
+        <v>Zohaann</v>
+      </c>
+      <c r="C26" t="str">
+        <f>HLOOKUP(A26,_xlfn.ANCHORARRAY(A$17),7,0)</f>
+        <v>Panruti</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="e">
+        <f t="shared" ref="B27:B31" si="0">HLOOKUP(A27,_xlfn.ANCHORARRAY(A$17),2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C27" t="e">
+        <f t="shared" ref="C27:C31" si="1">HLOOKUP(A27,_xlfn.ANCHORARRAY(A$17),7,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C28" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15">
+      <c r="A29" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>Madhavn</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="1"/>
+        <v>Cuddalore</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C30" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C31" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15">
+      <c r="A33" s="36" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15">
+      <c r="A34" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>414</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="str">
+        <f>LOOKUP(A35,rawdata!A$1:A$101,rawdata!B$1:B$101)</f>
+        <v>Zohaann</v>
+      </c>
+      <c r="C35" t="str">
+        <f>LOOKUP(A35,B$17:H$17,B$23:H$23)</f>
+        <v>Panruti</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" t="str">
+        <f>LOOKUP(A36,rawdata!A$1:A$101,rawdata!B$1:B$101)</f>
+        <v>Aditya</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" ref="C36:C40" si="2">LOOKUP(A36,B$17:H$17,B$23:H$23)</f>
+        <v>Cuddalore</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15">
+      <c r="A37" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="str">
+        <f>LOOKUP(A37,rawdata!A$1:A$101,rawdata!B$1:B$101)</f>
+        <v>Pranitn</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="2"/>
+        <v>Neyveli</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15">
+      <c r="A38" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="str">
+        <f>LOOKUP(A38,rawdata!A$1:A$101,rawdata!B$1:B$101)</f>
+        <v>Madhavn</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="2"/>
+        <v>Cuddalore</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="str">
+        <f>LOOKUP(A39,rawdata!A$1:A$101,rawdata!B$1:B$101)</f>
+        <v>Arjun</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="2"/>
+        <v>Cuddalore</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" t="str">
+        <f>LOOKUP(A40,rawdata!A$1:A$101,rawdata!B$1:B$101)</f>
+        <v>Mokshn</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="2"/>
+        <v>Cuddalore</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15">
+      <c r="A42" s="37" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15">
+      <c r="A43" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="B43" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="str">
+        <f>_xlfn.XLOOKUP(A44,rawdata!A$2:A$101,rawdata!B$2:B$101,"not found",0,1)</f>
+        <v>Zohaann</v>
+      </c>
+      <c r="C44" t="str">
+        <f>_xlfn.XLOOKUP(A44,B$17:H$17,B$23:H$23,"Not found",0,1)</f>
+        <v>Panruti</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="str">
+        <f>_xlfn.XLOOKUP(A45,rawdata!A$2:A$101,rawdata!B$2:B$101,"not found",0,1)</f>
+        <v>Aditya</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" ref="C45:C50" si="3">_xlfn.XLOOKUP(A45,B$17:H$17,B$23:H$23,"Not found",0,1)</f>
+        <v>Not found</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15">
+      <c r="A46" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="str">
+        <f>_xlfn.XLOOKUP(A46,rawdata!A$2:A$101,rawdata!B$2:B$101,"not found",0,1)</f>
+        <v>Pranitn</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="3"/>
+        <v>Neyveli</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15">
+      <c r="A47" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="str">
+        <f>_xlfn.XLOOKUP(A47,rawdata!A$2:A$101,rawdata!B$2:B$101,"not found",0,1)</f>
+        <v>Madhavn</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="3"/>
+        <v>Cuddalore</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="str">
+        <f>_xlfn.XLOOKUP(A48,rawdata!A$2:A$101,rawdata!B$2:B$101,"not found",0,1)</f>
+        <v>Arjun</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="3"/>
+        <v>Not found</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="str">
+        <f>_xlfn.XLOOKUP(A49,rawdata!A$2:A$101,rawdata!B$2:B$101,"not found",0,1)</f>
+        <v>Mokshn</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="3"/>
+        <v>Not found</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15">
+      <c r="A50" s="37" t="s">
+        <v>420</v>
+      </c>
+      <c r="B50" t="str">
+        <f>_xlfn.XLOOKUP(A50,rawdata!A$2:A$101,rawdata!B$2:B$101,"not found",0,1)</f>
+        <v>not found</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="3"/>
+        <v>Not found</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61636C7C-939C-4EB7-B320-38BDE0678E2E}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>421</v>
+      </c>
+      <c r="B1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>422</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>425</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="C4" s="74" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B6" t="str">
+        <f>INDEX(E6:I8,3,3)</f>
+        <v>i</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="73" t="s">
+        <v>427</v>
+      </c>
+      <c r="F6" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="G6" s="73" t="s">
+        <v>429</v>
+      </c>
+      <c r="H6" s="73" t="s">
+        <v>427</v>
+      </c>
+      <c r="I6" s="73" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" t="s">
+        <v>436</v>
+      </c>
+      <c r="B7" t="str">
+        <f>INDEX(E6:I6,1,3)</f>
+        <v>c</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>430</v>
+      </c>
+      <c r="F7" s="73" t="s">
+        <v>432</v>
+      </c>
+      <c r="G7" s="73" t="s">
+        <v>435</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>430</v>
+      </c>
+      <c r="I7" s="73" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15">
+      <c r="B8" t="str">
+        <f>INDEX(E6:E8,1,1)</f>
+        <v>a</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>442</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>431</v>
+      </c>
+      <c r="F8" s="73" t="s">
+        <v>433</v>
+      </c>
+      <c r="G8" s="73" t="s">
+        <v>434</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>431</v>
+      </c>
+      <c r="I8" s="73" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10">
+        <f>MATCH("f",E7:I7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="B11">
+        <f>MATCH("f",G6:G8,0)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" s="74" t="s">
+        <v>440</v>
+      </c>
+      <c r="B14">
+        <f>_xlfn.XMATCH("d",E7:I7,0,-1)</f>
+        <v>4</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="A16" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="E16" s="74" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" s="74" t="s">
+        <v>277</v>
+      </c>
+      <c r="B17" s="75">
+        <v>60000</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>451</v>
+      </c>
+      <c r="F17" s="74" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
+      <c r="A18" s="74" t="s">
+        <v>448</v>
+      </c>
+      <c r="B18">
+        <v>45000</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>452</v>
+      </c>
+      <c r="F18" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15">
+      <c r="A19" s="74" t="s">
+        <v>449</v>
+      </c>
+      <c r="B19">
+        <v>50000</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="F19">
+        <f>INDEX(B17:B20,MATCH(F18,A17:A20,0))</f>
+        <v>35000</v>
+      </c>
+      <c r="I19" s="74" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
+      <c r="A20" s="74" t="s">
+        <v>450</v>
+      </c>
+      <c r="B20">
+        <v>35000</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="E20" s="74" t="s">
+        <v>454</v>
+      </c>
+      <c r="F20">
+        <f>INDEX(C17:C20,MATCH(F18,A17:A20,0))</f>
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18" xr:uid="{95AD4801-87BE-47A1-B4E7-D7C0084C5C04}">
+      <formula1>$A$17:$A$20</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7A24AF-A89D-4410-B0AB-A75E15E06DC3}">
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="76" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2" t="s">
+        <v>460</v>
       </c>
       <c r="D2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>461</v>
+      </c>
+      <c r="E2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G2" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2" t="s">
+        <v>465</v>
+      </c>
+      <c r="I2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B3" t="s">
-        <v>247</v>
+        <v>468</v>
+      </c>
+      <c r="B3" s="52">
+        <v>46027</v>
+      </c>
+      <c r="C3" t="s">
+        <v>469</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>470</v>
+      </c>
+      <c r="E3" t="s">
+        <v>471</v>
+      </c>
+      <c r="F3" t="s">
+        <v>472</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>55000</v>
+      </c>
+      <c r="I3">
+        <v>110000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>474</v>
+      </c>
+      <c r="B4" s="52">
+        <v>46028</v>
+      </c>
+      <c r="C4" t="s">
+        <v>475</v>
+      </c>
       <c r="D4" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>476</v>
+      </c>
+      <c r="E4" t="s">
+        <v>477</v>
+      </c>
+      <c r="F4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>800</v>
+      </c>
+      <c r="I4">
+        <v>8000</v>
+      </c>
+      <c r="J4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B5" s="52">
+        <v>46029</v>
+      </c>
+      <c r="C5" t="s">
+        <v>481</v>
+      </c>
       <c r="D5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>482</v>
+      </c>
+      <c r="E5" t="s">
+        <v>483</v>
+      </c>
+      <c r="F5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>1500</v>
+      </c>
+      <c r="I5">
+        <v>7500</v>
+      </c>
+      <c r="J5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B6" s="52">
+        <v>46030</v>
+      </c>
+      <c r="C6" t="s">
+        <v>486</v>
+      </c>
       <c r="D6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>487</v>
+      </c>
+      <c r="E6" t="s">
+        <v>488</v>
+      </c>
+      <c r="F6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>12000</v>
+      </c>
+      <c r="I6">
+        <v>36000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" s="52">
+        <v>46031</v>
+      </c>
+      <c r="C7" t="s">
+        <v>469</v>
+      </c>
       <c r="D7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>476</v>
+      </c>
+      <c r="E7" t="s">
+        <v>490</v>
+      </c>
+      <c r="F7" t="s">
+        <v>472</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>18000</v>
+      </c>
+      <c r="I7">
+        <v>36000</v>
+      </c>
+      <c r="J7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" s="52">
+        <v>46032</v>
+      </c>
+      <c r="C8" t="s">
+        <v>475</v>
+      </c>
       <c r="D8" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>470</v>
+      </c>
+      <c r="E8" t="s">
+        <v>492</v>
+      </c>
+      <c r="F8" t="s">
+        <v>478</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>2500</v>
+      </c>
+      <c r="I8">
+        <v>20000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" s="52">
+        <v>46033</v>
+      </c>
+      <c r="C9" t="s">
+        <v>481</v>
+      </c>
       <c r="D9" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>487</v>
+      </c>
+      <c r="E9" t="s">
+        <v>471</v>
+      </c>
+      <c r="F9" t="s">
+        <v>472</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>55000</v>
+      </c>
+      <c r="I9">
+        <v>55000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>494</v>
+      </c>
+      <c r="B10" s="52">
+        <v>46034</v>
+      </c>
+      <c r="C10" t="s">
+        <v>486</v>
+      </c>
       <c r="D10" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>482</v>
+      </c>
+      <c r="E10" t="s">
+        <v>477</v>
+      </c>
+      <c r="F10" t="s">
+        <v>478</v>
+      </c>
+      <c r="G10">
+        <v>15</v>
+      </c>
+      <c r="H10">
+        <v>800</v>
+      </c>
+      <c r="I10">
+        <v>12000</v>
+      </c>
+      <c r="J10" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>495</v>
+      </c>
+      <c r="B11" s="52">
+        <v>46035</v>
+      </c>
+      <c r="C11" t="s">
+        <v>469</v>
+      </c>
       <c r="D11" t="s">
-        <v>256</v>
+        <v>482</v>
+      </c>
+      <c r="E11" t="s">
+        <v>488</v>
+      </c>
+      <c r="F11" t="s">
+        <v>472</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>12000</v>
+      </c>
+      <c r="I11">
+        <v>48000</v>
+      </c>
+      <c r="J11" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B12" s="52">
+        <v>46036</v>
+      </c>
+      <c r="C12" t="s">
+        <v>475</v>
+      </c>
+      <c r="D12" t="s">
+        <v>476</v>
+      </c>
+      <c r="E12" t="s">
+        <v>483</v>
+      </c>
+      <c r="F12" t="s">
+        <v>478</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>1500</v>
+      </c>
+      <c r="I12">
+        <v>10500</v>
+      </c>
+      <c r="J12" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>497</v>
+      </c>
+      <c r="B13" s="52">
+        <v>46037</v>
+      </c>
+      <c r="C13" t="s">
+        <v>481</v>
+      </c>
+      <c r="D13" t="s">
+        <v>470</v>
+      </c>
+      <c r="E13" t="s">
+        <v>490</v>
+      </c>
+      <c r="F13" t="s">
+        <v>472</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>18000</v>
+      </c>
+      <c r="I13">
+        <v>54000</v>
+      </c>
+      <c r="J13" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>498</v>
+      </c>
+      <c r="B14" s="52">
+        <v>46038</v>
+      </c>
+      <c r="C14" t="s">
+        <v>486</v>
+      </c>
+      <c r="D14" t="s">
+        <v>487</v>
+      </c>
+      <c r="E14" t="s">
+        <v>492</v>
+      </c>
+      <c r="F14" t="s">
+        <v>478</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="H14">
+        <v>2500</v>
+      </c>
+      <c r="I14">
+        <v>15000</v>
+      </c>
+      <c r="J14" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>499</v>
+      </c>
+      <c r="B15" s="52">
+        <v>46039</v>
+      </c>
+      <c r="C15" t="s">
+        <v>469</v>
+      </c>
+      <c r="D15" t="s">
+        <v>470</v>
+      </c>
+      <c r="E15" t="s">
+        <v>471</v>
+      </c>
+      <c r="F15" t="s">
+        <v>472</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>55000</v>
+      </c>
+      <c r="I15">
+        <v>165000</v>
+      </c>
+      <c r="J15" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>500</v>
+      </c>
+      <c r="B16" s="52">
+        <v>46040</v>
+      </c>
+      <c r="C16" t="s">
+        <v>475</v>
+      </c>
+      <c r="D16" t="s">
+        <v>482</v>
+      </c>
+      <c r="E16" t="s">
+        <v>477</v>
+      </c>
+      <c r="F16" t="s">
+        <v>478</v>
+      </c>
+      <c r="G16">
+        <v>20</v>
+      </c>
+      <c r="H16">
+        <v>800</v>
+      </c>
+      <c r="I16">
+        <v>16000</v>
+      </c>
+      <c r="J16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>501</v>
+      </c>
+      <c r="B17" s="52">
+        <v>46041</v>
+      </c>
+      <c r="C17" t="s">
+        <v>481</v>
+      </c>
+      <c r="D17" t="s">
+        <v>476</v>
+      </c>
+      <c r="E17" t="s">
+        <v>488</v>
+      </c>
+      <c r="F17" t="s">
+        <v>472</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>12000</v>
+      </c>
+      <c r="I17">
+        <v>24000</v>
+      </c>
+      <c r="J17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>502</v>
+      </c>
+      <c r="B18" s="52">
+        <v>46042</v>
+      </c>
+      <c r="C18" t="s">
+        <v>486</v>
+      </c>
+      <c r="D18" t="s">
+        <v>470</v>
+      </c>
+      <c r="E18" t="s">
+        <v>483</v>
+      </c>
+      <c r="F18" t="s">
+        <v>478</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>1500</v>
+      </c>
+      <c r="I18">
+        <v>15000</v>
+      </c>
+      <c r="J18" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>503</v>
+      </c>
+      <c r="B19" s="52">
+        <v>46043</v>
+      </c>
+      <c r="C19" t="s">
+        <v>469</v>
+      </c>
+      <c r="D19" t="s">
+        <v>487</v>
+      </c>
+      <c r="E19" t="s">
+        <v>490</v>
+      </c>
+      <c r="F19" t="s">
+        <v>472</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>18000</v>
+      </c>
+      <c r="I19">
+        <v>18000</v>
+      </c>
+      <c r="J19" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>504</v>
+      </c>
+      <c r="B20" s="52">
+        <v>46044</v>
+      </c>
+      <c r="C20" t="s">
+        <v>475</v>
+      </c>
+      <c r="D20" t="s">
+        <v>476</v>
+      </c>
+      <c r="E20" t="s">
+        <v>492</v>
+      </c>
+      <c r="F20" t="s">
+        <v>478</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>2500</v>
+      </c>
+      <c r="I20">
+        <v>30000</v>
+      </c>
+      <c r="J20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>505</v>
+      </c>
+      <c r="B21" s="52">
+        <v>46045</v>
+      </c>
+      <c r="C21" t="s">
+        <v>481</v>
+      </c>
+      <c r="D21" t="s">
+        <v>482</v>
+      </c>
+      <c r="E21" t="s">
+        <v>471</v>
+      </c>
+      <c r="F21" t="s">
+        <v>472</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>55000</v>
+      </c>
+      <c r="I21">
+        <v>110000</v>
+      </c>
+      <c r="J21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>506</v>
+      </c>
+      <c r="B22" s="52">
+        <v>46046</v>
+      </c>
+      <c r="C22" t="s">
+        <v>486</v>
+      </c>
+      <c r="D22" t="s">
+        <v>470</v>
+      </c>
+      <c r="E22" t="s">
+        <v>477</v>
+      </c>
+      <c r="F22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G22">
+        <v>18</v>
+      </c>
+      <c r="H22">
+        <v>800</v>
+      </c>
+      <c r="I22">
+        <v>14400</v>
+      </c>
+      <c r="J22" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>507</v>
+      </c>
+      <c r="B23" s="52">
+        <v>46047</v>
+      </c>
+      <c r="C23" t="s">
+        <v>469</v>
+      </c>
+      <c r="D23" t="s">
+        <v>476</v>
+      </c>
+      <c r="E23" t="s">
+        <v>488</v>
+      </c>
+      <c r="F23" t="s">
+        <v>472</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23">
+        <v>12000</v>
+      </c>
+      <c r="I23">
+        <v>60000</v>
+      </c>
+      <c r="J23" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>508</v>
+      </c>
+      <c r="B24" s="52">
+        <v>46048</v>
+      </c>
+      <c r="C24" t="s">
+        <v>475</v>
+      </c>
+      <c r="D24" t="s">
+        <v>487</v>
+      </c>
+      <c r="E24" t="s">
+        <v>483</v>
+      </c>
+      <c r="F24" t="s">
+        <v>478</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24">
+        <v>1500</v>
+      </c>
+      <c r="I24">
+        <v>13500</v>
+      </c>
+      <c r="J24" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>509</v>
+      </c>
+      <c r="B25" s="52">
+        <v>46049</v>
+      </c>
+      <c r="C25" t="s">
+        <v>481</v>
+      </c>
+      <c r="D25" t="s">
+        <v>470</v>
+      </c>
+      <c r="E25" t="s">
+        <v>490</v>
+      </c>
+      <c r="F25" t="s">
+        <v>472</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>18000</v>
+      </c>
+      <c r="I25">
+        <v>36000</v>
+      </c>
+      <c r="J25" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>510</v>
+      </c>
+      <c r="B26" s="52">
+        <v>46050</v>
+      </c>
+      <c r="C26" t="s">
+        <v>486</v>
+      </c>
+      <c r="D26" t="s">
+        <v>482</v>
+      </c>
+      <c r="E26" t="s">
+        <v>492</v>
+      </c>
+      <c r="F26" t="s">
+        <v>478</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+      <c r="H26">
+        <v>2500</v>
+      </c>
+      <c r="I26">
+        <v>25000</v>
+      </c>
+      <c r="J26" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>511</v>
+      </c>
+      <c r="B27" s="52">
+        <v>46051</v>
+      </c>
+      <c r="C27" t="s">
+        <v>469</v>
+      </c>
+      <c r="D27" t="s">
+        <v>482</v>
+      </c>
+      <c r="E27" t="s">
+        <v>471</v>
+      </c>
+      <c r="F27" t="s">
+        <v>472</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>55000</v>
+      </c>
+      <c r="I27">
+        <v>55000</v>
+      </c>
+      <c r="J27" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>512</v>
+      </c>
+      <c r="B28" s="52">
+        <v>46052</v>
+      </c>
+      <c r="C28" t="s">
+        <v>475</v>
+      </c>
+      <c r="D28" t="s">
+        <v>476</v>
+      </c>
+      <c r="E28" t="s">
+        <v>477</v>
+      </c>
+      <c r="F28" t="s">
+        <v>478</v>
+      </c>
+      <c r="G28">
+        <v>25</v>
+      </c>
+      <c r="H28">
+        <v>800</v>
+      </c>
+      <c r="I28">
+        <v>20000</v>
+      </c>
+      <c r="J28" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>513</v>
+      </c>
+      <c r="B29" s="52">
+        <v>46053</v>
+      </c>
+      <c r="C29" t="s">
+        <v>481</v>
+      </c>
+      <c r="D29" t="s">
+        <v>487</v>
+      </c>
+      <c r="E29" t="s">
+        <v>488</v>
+      </c>
+      <c r="F29" t="s">
+        <v>472</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29">
+        <v>12000</v>
+      </c>
+      <c r="I29">
+        <v>36000</v>
+      </c>
+      <c r="J29" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>514</v>
+      </c>
+      <c r="B30" s="52">
+        <v>46054</v>
+      </c>
+      <c r="C30" t="s">
+        <v>486</v>
+      </c>
+      <c r="D30" t="s">
+        <v>470</v>
+      </c>
+      <c r="E30" t="s">
+        <v>483</v>
+      </c>
+      <c r="F30" t="s">
+        <v>478</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>1500</v>
+      </c>
+      <c r="I30">
+        <v>12000</v>
+      </c>
+      <c r="J30" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>515</v>
+      </c>
+      <c r="B31" s="52">
+        <v>46055</v>
+      </c>
+      <c r="C31" t="s">
+        <v>469</v>
+      </c>
+      <c r="D31" t="s">
+        <v>487</v>
+      </c>
+      <c r="E31" t="s">
+        <v>490</v>
+      </c>
+      <c r="F31" t="s">
+        <v>472</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>18000</v>
+      </c>
+      <c r="I31">
+        <v>72000</v>
+      </c>
+      <c r="J31" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B32" s="52">
+        <v>46056</v>
+      </c>
+      <c r="C32" t="s">
+        <v>475</v>
+      </c>
+      <c r="D32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E32" t="s">
+        <v>492</v>
+      </c>
+      <c r="F32" t="s">
+        <v>478</v>
+      </c>
+      <c r="G32">
+        <v>15</v>
+      </c>
+      <c r="H32">
+        <v>2500</v>
+      </c>
+      <c r="I32">
+        <v>37500</v>
+      </c>
+      <c r="J32" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>517</v>
+      </c>
+      <c r="B33" s="52">
+        <v>46057</v>
+      </c>
+      <c r="C33" t="s">
+        <v>481</v>
+      </c>
+      <c r="D33" t="s">
+        <v>476</v>
+      </c>
+      <c r="E33" t="s">
+        <v>471</v>
+      </c>
+      <c r="F33" t="s">
+        <v>472</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>55000</v>
+      </c>
+      <c r="I33">
+        <v>110000</v>
+      </c>
+      <c r="J33" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>518</v>
+      </c>
+      <c r="B34" s="52">
+        <v>46058</v>
+      </c>
+      <c r="C34" t="s">
+        <v>486</v>
+      </c>
+      <c r="D34" t="s">
+        <v>470</v>
+      </c>
+      <c r="E34" t="s">
+        <v>477</v>
+      </c>
+      <c r="F34" t="s">
+        <v>478</v>
+      </c>
+      <c r="G34">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <v>800</v>
+      </c>
+      <c r="I34">
+        <v>16000</v>
+      </c>
+      <c r="J34" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>519</v>
+      </c>
+      <c r="B35" s="52">
+        <v>46059</v>
+      </c>
+      <c r="C35" t="s">
+        <v>469</v>
+      </c>
+      <c r="D35" t="s">
+        <v>482</v>
+      </c>
+      <c r="E35" t="s">
+        <v>488</v>
+      </c>
+      <c r="F35" t="s">
+        <v>472</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>12000</v>
+      </c>
+      <c r="I35">
+        <v>24000</v>
+      </c>
+      <c r="J35" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>520</v>
+      </c>
+      <c r="B36" s="52">
+        <v>46060</v>
+      </c>
+      <c r="C36" t="s">
+        <v>475</v>
+      </c>
+      <c r="D36" t="s">
+        <v>487</v>
+      </c>
+      <c r="E36" t="s">
+        <v>483</v>
+      </c>
+      <c r="F36" t="s">
+        <v>478</v>
+      </c>
+      <c r="G36">
+        <v>12</v>
+      </c>
+      <c r="H36">
+        <v>1500</v>
+      </c>
+      <c r="I36">
+        <v>18000</v>
+      </c>
+      <c r="J36" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>521</v>
+      </c>
+      <c r="B37" s="52">
+        <v>46061</v>
+      </c>
+      <c r="C37" t="s">
+        <v>481</v>
+      </c>
+      <c r="D37" t="s">
+        <v>470</v>
+      </c>
+      <c r="E37" t="s">
+        <v>490</v>
+      </c>
+      <c r="F37" t="s">
+        <v>472</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <v>18000</v>
+      </c>
+      <c r="I37">
+        <v>54000</v>
+      </c>
+      <c r="J37" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>522</v>
+      </c>
+      <c r="B38" s="52">
+        <v>46062</v>
+      </c>
+      <c r="C38" t="s">
+        <v>486</v>
+      </c>
+      <c r="D38" t="s">
+        <v>476</v>
+      </c>
+      <c r="E38" t="s">
+        <v>492</v>
+      </c>
+      <c r="F38" t="s">
+        <v>478</v>
+      </c>
+      <c r="G38">
+        <v>7</v>
+      </c>
+      <c r="H38">
+        <v>2500</v>
+      </c>
+      <c r="I38">
+        <v>17500</v>
+      </c>
+      <c r="J38" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>523</v>
+      </c>
+      <c r="B39" s="52">
+        <v>46063</v>
+      </c>
+      <c r="C39" t="s">
+        <v>469</v>
+      </c>
+      <c r="D39" t="s">
+        <v>476</v>
+      </c>
+      <c r="E39" t="s">
+        <v>471</v>
+      </c>
+      <c r="F39" t="s">
+        <v>472</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>55000</v>
+      </c>
+      <c r="I39">
+        <v>110000</v>
+      </c>
+      <c r="J39" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>524</v>
+      </c>
+      <c r="B40" s="52">
+        <v>46064</v>
+      </c>
+      <c r="C40" t="s">
+        <v>475</v>
+      </c>
+      <c r="D40" t="s">
+        <v>482</v>
+      </c>
+      <c r="E40" t="s">
+        <v>477</v>
+      </c>
+      <c r="F40" t="s">
+        <v>478</v>
+      </c>
+      <c r="G40">
+        <v>30</v>
+      </c>
+      <c r="H40">
+        <v>800</v>
+      </c>
+      <c r="I40">
+        <v>24000</v>
+      </c>
+      <c r="J40" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>525</v>
+      </c>
+      <c r="B41" s="52">
+        <v>46065</v>
+      </c>
+      <c r="C41" t="s">
+        <v>481</v>
+      </c>
+      <c r="D41" t="s">
+        <v>487</v>
+      </c>
+      <c r="E41" t="s">
+        <v>488</v>
+      </c>
+      <c r="F41" t="s">
+        <v>472</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>12000</v>
+      </c>
+      <c r="I41">
+        <v>48000</v>
+      </c>
+      <c r="J41" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>526</v>
+      </c>
+      <c r="B42" s="52">
+        <v>46066</v>
+      </c>
+      <c r="C42" t="s">
+        <v>486</v>
+      </c>
+      <c r="D42" t="s">
+        <v>470</v>
+      </c>
+      <c r="E42" t="s">
+        <v>483</v>
+      </c>
+      <c r="F42" t="s">
+        <v>478</v>
+      </c>
+      <c r="G42">
+        <v>15</v>
+      </c>
+      <c r="H42">
+        <v>1500</v>
+      </c>
+      <c r="I42">
+        <v>22500</v>
+      </c>
+      <c r="J42" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>527</v>
+      </c>
+      <c r="B43" s="52">
+        <v>46067</v>
+      </c>
+      <c r="C43" t="s">
+        <v>469</v>
+      </c>
+      <c r="D43" t="s">
+        <v>470</v>
+      </c>
+      <c r="E43" t="s">
+        <v>490</v>
+      </c>
+      <c r="F43" t="s">
+        <v>472</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43">
+        <v>18000</v>
+      </c>
+      <c r="I43">
+        <v>36000</v>
+      </c>
+      <c r="J43" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>528</v>
+      </c>
+      <c r="B44" s="52">
+        <v>46068</v>
+      </c>
+      <c r="C44" t="s">
+        <v>475</v>
+      </c>
+      <c r="D44" t="s">
+        <v>476</v>
+      </c>
+      <c r="E44" t="s">
+        <v>492</v>
+      </c>
+      <c r="F44" t="s">
+        <v>478</v>
+      </c>
+      <c r="G44">
+        <v>10</v>
+      </c>
+      <c r="H44">
+        <v>2500</v>
+      </c>
+      <c r="I44">
+        <v>25000</v>
+      </c>
+      <c r="J44" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>529</v>
+      </c>
+      <c r="B45" s="52">
+        <v>46069</v>
+      </c>
+      <c r="C45" t="s">
+        <v>481</v>
+      </c>
+      <c r="D45" t="s">
+        <v>482</v>
+      </c>
+      <c r="E45" t="s">
+        <v>471</v>
+      </c>
+      <c r="F45" t="s">
+        <v>472</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="H45">
+        <v>55000</v>
+      </c>
+      <c r="I45">
+        <v>165000</v>
+      </c>
+      <c r="J45" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>530</v>
+      </c>
+      <c r="B46" s="52">
+        <v>46070</v>
+      </c>
+      <c r="C46" t="s">
+        <v>486</v>
+      </c>
+      <c r="D46" t="s">
+        <v>487</v>
+      </c>
+      <c r="E46" t="s">
+        <v>477</v>
+      </c>
+      <c r="F46" t="s">
+        <v>478</v>
+      </c>
+      <c r="G46">
+        <v>22</v>
+      </c>
+      <c r="H46">
+        <v>800</v>
+      </c>
+      <c r="I46">
+        <v>17600</v>
+      </c>
+      <c r="J46" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>531</v>
+      </c>
+      <c r="B47" s="52">
+        <v>46071</v>
+      </c>
+      <c r="C47" t="s">
+        <v>469</v>
+      </c>
+      <c r="D47" t="s">
+        <v>482</v>
+      </c>
+      <c r="E47" t="s">
+        <v>488</v>
+      </c>
+      <c r="F47" t="s">
+        <v>472</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+      <c r="H47">
+        <v>12000</v>
+      </c>
+      <c r="I47">
+        <v>60000</v>
+      </c>
+      <c r="J47" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>532</v>
+      </c>
+      <c r="B48" s="52">
+        <v>46072</v>
+      </c>
+      <c r="C48" t="s">
+        <v>475</v>
+      </c>
+      <c r="D48" t="s">
+        <v>470</v>
+      </c>
+      <c r="E48" t="s">
+        <v>483</v>
+      </c>
+      <c r="F48" t="s">
+        <v>478</v>
+      </c>
+      <c r="G48">
+        <v>11</v>
+      </c>
+      <c r="H48">
+        <v>1500</v>
+      </c>
+      <c r="I48">
+        <v>16500</v>
+      </c>
+      <c r="J48" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>533</v>
+      </c>
+      <c r="B49" s="52">
+        <v>46073</v>
+      </c>
+      <c r="C49" t="s">
+        <v>481</v>
+      </c>
+      <c r="D49" t="s">
+        <v>476</v>
+      </c>
+      <c r="E49" t="s">
+        <v>490</v>
+      </c>
+      <c r="F49" t="s">
+        <v>472</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>18000</v>
+      </c>
+      <c r="I49">
+        <v>36000</v>
+      </c>
+      <c r="J49" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>534</v>
+      </c>
+      <c r="B50" s="52">
+        <v>46074</v>
+      </c>
+      <c r="C50" t="s">
+        <v>486</v>
+      </c>
+      <c r="D50" t="s">
+        <v>487</v>
+      </c>
+      <c r="E50" t="s">
+        <v>492</v>
+      </c>
+      <c r="F50" t="s">
+        <v>478</v>
+      </c>
+      <c r="G50">
+        <v>9</v>
+      </c>
+      <c r="H50">
+        <v>2500</v>
+      </c>
+      <c r="I50">
+        <v>22500</v>
+      </c>
+      <c r="J50" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>535</v>
+      </c>
+      <c r="B51" s="52">
+        <v>46075</v>
+      </c>
+      <c r="C51" t="s">
+        <v>469</v>
+      </c>
+      <c r="D51" t="s">
+        <v>487</v>
+      </c>
+      <c r="E51" t="s">
+        <v>471</v>
+      </c>
+      <c r="F51" t="s">
+        <v>472</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>55000</v>
+      </c>
+      <c r="I51">
+        <v>110000</v>
+      </c>
+      <c r="J51" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>536</v>
+      </c>
+      <c r="B52" s="52">
+        <v>46076</v>
+      </c>
+      <c r="C52" t="s">
+        <v>475</v>
+      </c>
+      <c r="D52" t="s">
+        <v>482</v>
+      </c>
+      <c r="E52" t="s">
+        <v>477</v>
+      </c>
+      <c r="F52" t="s">
+        <v>478</v>
+      </c>
+      <c r="G52">
+        <v>28</v>
+      </c>
+      <c r="H52">
+        <v>800</v>
+      </c>
+      <c r="I52">
+        <v>22400</v>
+      </c>
+      <c r="J52" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -4837,125 +8432,1694 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F700E6B1-D1A5-4261-AFA3-01D0C2A0EAD0}">
-  <dimension ref="A1:D16"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE70BBDA-F4D4-440D-8F0F-006044A20BEE}">
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="76" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="B1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>459</v>
+      </c>
+      <c r="C1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F1" t="s">
+        <v>463</v>
+      </c>
+      <c r="G1" t="s">
+        <v>464</v>
+      </c>
+      <c r="H1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I1" t="s">
+        <v>466</v>
+      </c>
+      <c r="J1" t="s">
+        <v>467</v>
+      </c>
+      <c r="M1" s="76" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B2" s="52">
+        <v>46027</v>
+      </c>
+      <c r="C2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>55000</v>
+      </c>
+      <c r="I2">
+        <v>110000</v>
+      </c>
+      <c r="J2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M2" s="76" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B3" s="52">
+        <v>46028</v>
+      </c>
+      <c r="C3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E3" t="s">
+        <v>477</v>
+      </c>
+      <c r="F3" t="s">
+        <v>478</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>800</v>
+      </c>
+      <c r="I3">
+        <v>8000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>479</v>
+      </c>
+      <c r="M3" s="76" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B4" s="52">
+        <v>46029</v>
+      </c>
+      <c r="C4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E4" t="s">
+        <v>483</v>
+      </c>
+      <c r="F4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>1500</v>
+      </c>
+      <c r="I4">
+        <v>7500</v>
+      </c>
+      <c r="J4" t="s">
+        <v>484</v>
+      </c>
+      <c r="M4" s="76" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" s="52">
+        <v>46030</v>
+      </c>
+      <c r="C5" t="s">
+        <v>486</v>
+      </c>
+      <c r="D5" t="s">
+        <v>487</v>
+      </c>
+      <c r="E5" t="s">
+        <v>488</v>
+      </c>
+      <c r="F5" t="s">
+        <v>472</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>12000</v>
+      </c>
+      <c r="I5">
+        <v>36000</v>
+      </c>
+      <c r="J5" t="s">
+        <v>473</v>
+      </c>
+      <c r="M5" s="76" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>489</v>
+      </c>
+      <c r="B6" s="52">
+        <v>46031</v>
+      </c>
+      <c r="C6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D6" t="s">
+        <v>476</v>
+      </c>
+      <c r="E6" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>18000</v>
+      </c>
+      <c r="I6">
+        <v>36000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>479</v>
+      </c>
+      <c r="M6" s="76" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>491</v>
+      </c>
+      <c r="B7" s="52">
+        <v>46032</v>
+      </c>
+      <c r="C7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E7" t="s">
+        <v>492</v>
+      </c>
+      <c r="F7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>2500</v>
+      </c>
+      <c r="I7">
+        <v>20000</v>
+      </c>
+      <c r="J7" t="s">
+        <v>473</v>
+      </c>
+      <c r="M7" s="76" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>493</v>
+      </c>
+      <c r="B8" s="52">
+        <v>46033</v>
+      </c>
+      <c r="C8" t="s">
+        <v>481</v>
+      </c>
+      <c r="D8" t="s">
+        <v>487</v>
+      </c>
+      <c r="E8" t="s">
+        <v>471</v>
+      </c>
+      <c r="F8" t="s">
+        <v>472</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>55000</v>
+      </c>
+      <c r="I8">
+        <v>55000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>479</v>
+      </c>
+      <c r="M8" s="76" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B9" s="52">
+        <v>46034</v>
+      </c>
+      <c r="C9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E9" t="s">
+        <v>477</v>
+      </c>
+      <c r="F9" t="s">
+        <v>478</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>800</v>
+      </c>
+      <c r="I9">
+        <v>12000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>484</v>
+      </c>
+      <c r="M9" s="76" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" s="52">
+        <v>46035</v>
+      </c>
+      <c r="C10" t="s">
+        <v>469</v>
+      </c>
+      <c r="D10" t="s">
+        <v>482</v>
+      </c>
+      <c r="E10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F10" t="s">
+        <v>472</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>12000</v>
+      </c>
+      <c r="I10">
+        <v>48000</v>
+      </c>
+      <c r="J10" t="s">
+        <v>473</v>
+      </c>
+      <c r="M10" s="76" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>496</v>
+      </c>
+      <c r="B11" s="52">
+        <v>46036</v>
+      </c>
+      <c r="C11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D11" t="s">
+        <v>476</v>
+      </c>
+      <c r="E11" t="s">
+        <v>483</v>
+      </c>
+      <c r="F11" t="s">
+        <v>478</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+      <c r="H11">
+        <v>1500</v>
+      </c>
+      <c r="I11">
+        <v>10500</v>
+      </c>
+      <c r="J11" t="s">
+        <v>479</v>
+      </c>
+      <c r="M11" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>497</v>
+      </c>
+      <c r="B12" s="52">
+        <v>46037</v>
+      </c>
+      <c r="C12" t="s">
+        <v>481</v>
+      </c>
+      <c r="D12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E12" t="s">
+        <v>490</v>
+      </c>
+      <c r="F12" t="s">
+        <v>472</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <v>18000</v>
+      </c>
+      <c r="I12">
+        <v>54000</v>
+      </c>
+      <c r="J12" t="s">
+        <v>473</v>
+      </c>
+      <c r="M12" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="52">
+        <v>46038</v>
+      </c>
+      <c r="C13" t="s">
+        <v>486</v>
+      </c>
+      <c r="D13" t="s">
+        <v>487</v>
+      </c>
+      <c r="E13" t="s">
+        <v>492</v>
+      </c>
+      <c r="F13" t="s">
+        <v>478</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>2500</v>
+      </c>
+      <c r="I13">
+        <v>15000</v>
+      </c>
+      <c r="J13" t="s">
+        <v>484</v>
+      </c>
+      <c r="M13" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>499</v>
+      </c>
+      <c r="B14" s="52">
+        <v>46039</v>
+      </c>
+      <c r="C14" t="s">
+        <v>469</v>
+      </c>
+      <c r="D14" t="s">
+        <v>470</v>
+      </c>
+      <c r="E14" t="s">
+        <v>471</v>
+      </c>
+      <c r="F14" t="s">
+        <v>472</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>55000</v>
+      </c>
+      <c r="I14">
+        <v>165000</v>
+      </c>
+      <c r="J14" t="s">
+        <v>479</v>
+      </c>
+      <c r="M14" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="52">
+        <v>46040</v>
+      </c>
+      <c r="C15" t="s">
+        <v>475</v>
+      </c>
+      <c r="D15" t="s">
+        <v>482</v>
+      </c>
+      <c r="E15" t="s">
+        <v>477</v>
+      </c>
+      <c r="F15" t="s">
+        <v>478</v>
+      </c>
+      <c r="G15">
+        <v>20</v>
+      </c>
+      <c r="H15">
+        <v>800</v>
+      </c>
+      <c r="I15">
+        <v>16000</v>
+      </c>
+      <c r="J15" t="s">
+        <v>473</v>
+      </c>
+      <c r="M15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>501</v>
+      </c>
+      <c r="B16" s="52">
+        <v>46041</v>
+      </c>
+      <c r="C16" t="s">
+        <v>481</v>
+      </c>
+      <c r="D16" t="s">
+        <v>476</v>
+      </c>
+      <c r="E16" t="s">
+        <v>488</v>
+      </c>
+      <c r="F16" t="s">
+        <v>472</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>12000</v>
+      </c>
+      <c r="I16">
+        <v>24000</v>
+      </c>
+      <c r="J16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>502</v>
+      </c>
+      <c r="B17" s="52">
+        <v>46042</v>
+      </c>
+      <c r="C17" t="s">
+        <v>486</v>
+      </c>
+      <c r="D17" t="s">
+        <v>470</v>
+      </c>
+      <c r="E17" t="s">
+        <v>483</v>
+      </c>
+      <c r="F17" t="s">
+        <v>478</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>1500</v>
+      </c>
+      <c r="I17">
+        <v>15000</v>
+      </c>
+      <c r="J17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>503</v>
+      </c>
+      <c r="B18" s="52">
+        <v>46043</v>
+      </c>
+      <c r="C18" t="s">
+        <v>469</v>
+      </c>
+      <c r="D18" t="s">
+        <v>487</v>
+      </c>
+      <c r="E18" t="s">
+        <v>490</v>
+      </c>
+      <c r="F18" t="s">
+        <v>472</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>18000</v>
+      </c>
+      <c r="I18">
+        <v>18000</v>
+      </c>
+      <c r="J18" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>504</v>
+      </c>
+      <c r="B19" s="52">
+        <v>46044</v>
+      </c>
+      <c r="C19" t="s">
+        <v>475</v>
+      </c>
+      <c r="D19" t="s">
+        <v>476</v>
+      </c>
+      <c r="E19" t="s">
+        <v>492</v>
+      </c>
+      <c r="F19" t="s">
+        <v>478</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <v>2500</v>
+      </c>
+      <c r="I19">
+        <v>30000</v>
+      </c>
+      <c r="J19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>505</v>
+      </c>
+      <c r="B20" s="52">
+        <v>46045</v>
+      </c>
+      <c r="C20" t="s">
+        <v>481</v>
+      </c>
+      <c r="D20" t="s">
+        <v>482</v>
+      </c>
+      <c r="E20" t="s">
+        <v>471</v>
+      </c>
+      <c r="F20" t="s">
+        <v>472</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>55000</v>
+      </c>
+      <c r="I20">
+        <v>110000</v>
+      </c>
+      <c r="J20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>506</v>
+      </c>
+      <c r="B21" s="52">
+        <v>46046</v>
+      </c>
+      <c r="C21" t="s">
+        <v>486</v>
+      </c>
+      <c r="D21" t="s">
+        <v>470</v>
+      </c>
+      <c r="E21" t="s">
+        <v>477</v>
+      </c>
+      <c r="F21" t="s">
+        <v>478</v>
+      </c>
+      <c r="G21">
         <v>18</v>
       </c>
-      <c r="B2" t="str">
-        <f>VLOOKUP(A:A,Sheet1!A:B,2,1)</f>
-        <v>Zohaann</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" t="str">
-        <f>VLOOKUP(A:A,Sheet1!A:B,2,1)</f>
-        <v>Aditya</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" t="str">
-        <f>VLOOKUP(A:A,Sheet1!A:B,2,1)</f>
-        <v>Rudra</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" t="str">
-        <f>VLOOKUP(A:A,Sheet1!A:B,2,1)</f>
-        <v>Shlok</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" t="str">
-        <f>VLOOKUP(A:A,Sheet1!A:B,2,1)</f>
-        <v>Arjun</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="str">
-        <f>VLOOKUP(A:A,Sheet1!A:B,2,1)</f>
-        <v>Mokshn</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" t="str">
-        <f>VLOOKUP(A:A,Sheet1!A:B,2,1)</f>
-        <v>Tanishn</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>259</v>
-      </c>
-      <c r="B14" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" t="s">
-        <v>263</v>
-      </c>
-      <c r="D14" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>260</v>
-      </c>
-      <c r="B15">
-        <v>1200</v>
-      </c>
-      <c r="C15">
-        <v>2000</v>
-      </c>
-      <c r="D15">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>261</v>
-      </c>
-      <c r="B16">
+      <c r="H21">
+        <v>800</v>
+      </c>
+      <c r="I21">
+        <v>14400</v>
+      </c>
+      <c r="J21" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>507</v>
+      </c>
+      <c r="B22" s="52">
+        <v>46047</v>
+      </c>
+      <c r="C22" t="s">
+        <v>469</v>
+      </c>
+      <c r="D22" t="s">
+        <v>476</v>
+      </c>
+      <c r="E22" t="s">
+        <v>488</v>
+      </c>
+      <c r="F22" t="s">
+        <v>472</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22">
+        <v>12000</v>
+      </c>
+      <c r="I22">
+        <v>60000</v>
+      </c>
+      <c r="J22" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>508</v>
+      </c>
+      <c r="B23" s="52">
+        <v>46048</v>
+      </c>
+      <c r="C23" t="s">
+        <v>475</v>
+      </c>
+      <c r="D23" t="s">
+        <v>487</v>
+      </c>
+      <c r="E23" t="s">
+        <v>483</v>
+      </c>
+      <c r="F23" t="s">
+        <v>478</v>
+      </c>
+      <c r="G23">
+        <v>9</v>
+      </c>
+      <c r="H23">
+        <v>1500</v>
+      </c>
+      <c r="I23">
+        <v>13500</v>
+      </c>
+      <c r="J23" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>509</v>
+      </c>
+      <c r="B24" s="52">
+        <v>46049</v>
+      </c>
+      <c r="C24" t="s">
+        <v>481</v>
+      </c>
+      <c r="D24" t="s">
+        <v>470</v>
+      </c>
+      <c r="E24" t="s">
+        <v>490</v>
+      </c>
+      <c r="F24" t="s">
+        <v>472</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>18000</v>
+      </c>
+      <c r="I24">
+        <v>36000</v>
+      </c>
+      <c r="J24" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>510</v>
+      </c>
+      <c r="B25" s="52">
+        <v>46050</v>
+      </c>
+      <c r="C25" t="s">
+        <v>486</v>
+      </c>
+      <c r="D25" t="s">
+        <v>482</v>
+      </c>
+      <c r="E25" t="s">
+        <v>492</v>
+      </c>
+      <c r="F25" t="s">
+        <v>478</v>
+      </c>
+      <c r="G25">
         <v>10</v>
       </c>
-      <c r="C16">
+      <c r="H25">
+        <v>2500</v>
+      </c>
+      <c r="I25">
+        <v>25000</v>
+      </c>
+      <c r="J25" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>511</v>
+      </c>
+      <c r="B26" s="52">
+        <v>46051</v>
+      </c>
+      <c r="C26" t="s">
+        <v>469</v>
+      </c>
+      <c r="D26" t="s">
+        <v>482</v>
+      </c>
+      <c r="E26" t="s">
+        <v>471</v>
+      </c>
+      <c r="F26" t="s">
+        <v>472</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>55000</v>
+      </c>
+      <c r="I26">
+        <v>55000</v>
+      </c>
+      <c r="J26" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>512</v>
+      </c>
+      <c r="B27" s="52">
+        <v>46052</v>
+      </c>
+      <c r="C27" t="s">
+        <v>475</v>
+      </c>
+      <c r="D27" t="s">
+        <v>476</v>
+      </c>
+      <c r="E27" t="s">
+        <v>477</v>
+      </c>
+      <c r="F27" t="s">
+        <v>478</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
+      </c>
+      <c r="H27">
+        <v>800</v>
+      </c>
+      <c r="I27">
+        <v>20000</v>
+      </c>
+      <c r="J27" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>513</v>
+      </c>
+      <c r="B28" s="52">
+        <v>46053</v>
+      </c>
+      <c r="C28" t="s">
+        <v>481</v>
+      </c>
+      <c r="D28" t="s">
+        <v>487</v>
+      </c>
+      <c r="E28" t="s">
+        <v>488</v>
+      </c>
+      <c r="F28" t="s">
+        <v>472</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>12000</v>
+      </c>
+      <c r="I28">
+        <v>36000</v>
+      </c>
+      <c r="J28" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>514</v>
+      </c>
+      <c r="B29" s="52">
+        <v>46054</v>
+      </c>
+      <c r="C29" t="s">
+        <v>486</v>
+      </c>
+      <c r="D29" t="s">
+        <v>470</v>
+      </c>
+      <c r="E29" t="s">
+        <v>483</v>
+      </c>
+      <c r="F29" t="s">
+        <v>478</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>1500</v>
+      </c>
+      <c r="I29">
+        <v>12000</v>
+      </c>
+      <c r="J29" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>515</v>
+      </c>
+      <c r="B30" s="52">
+        <v>46055</v>
+      </c>
+      <c r="C30" t="s">
+        <v>469</v>
+      </c>
+      <c r="D30" t="s">
+        <v>487</v>
+      </c>
+      <c r="E30" t="s">
+        <v>490</v>
+      </c>
+      <c r="F30" t="s">
+        <v>472</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>18000</v>
+      </c>
+      <c r="I30">
+        <v>72000</v>
+      </c>
+      <c r="J30" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>516</v>
+      </c>
+      <c r="B31" s="52">
+        <v>46056</v>
+      </c>
+      <c r="C31" t="s">
+        <v>475</v>
+      </c>
+      <c r="D31" t="s">
+        <v>482</v>
+      </c>
+      <c r="E31" t="s">
+        <v>492</v>
+      </c>
+      <c r="F31" t="s">
+        <v>478</v>
+      </c>
+      <c r="G31">
+        <v>15</v>
+      </c>
+      <c r="H31">
+        <v>2500</v>
+      </c>
+      <c r="I31">
+        <v>37500</v>
+      </c>
+      <c r="J31" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>517</v>
+      </c>
+      <c r="B32" s="52">
+        <v>46057</v>
+      </c>
+      <c r="C32" t="s">
+        <v>481</v>
+      </c>
+      <c r="D32" t="s">
+        <v>476</v>
+      </c>
+      <c r="E32" t="s">
+        <v>471</v>
+      </c>
+      <c r="F32" t="s">
+        <v>472</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <v>55000</v>
+      </c>
+      <c r="I32">
+        <v>110000</v>
+      </c>
+      <c r="J32" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>518</v>
+      </c>
+      <c r="B33" s="52">
+        <v>46058</v>
+      </c>
+      <c r="C33" t="s">
+        <v>486</v>
+      </c>
+      <c r="D33" t="s">
+        <v>470</v>
+      </c>
+      <c r="E33" t="s">
+        <v>477</v>
+      </c>
+      <c r="F33" t="s">
+        <v>478</v>
+      </c>
+      <c r="G33">
+        <v>20</v>
+      </c>
+      <c r="H33">
+        <v>800</v>
+      </c>
+      <c r="I33">
+        <v>16000</v>
+      </c>
+      <c r="J33" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>519</v>
+      </c>
+      <c r="B34" s="52">
+        <v>46059</v>
+      </c>
+      <c r="C34" t="s">
+        <v>469</v>
+      </c>
+      <c r="D34" t="s">
+        <v>482</v>
+      </c>
+      <c r="E34" t="s">
+        <v>488</v>
+      </c>
+      <c r="F34" t="s">
+        <v>472</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>12000</v>
+      </c>
+      <c r="I34">
+        <v>24000</v>
+      </c>
+      <c r="J34" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>520</v>
+      </c>
+      <c r="B35" s="52">
+        <v>46060</v>
+      </c>
+      <c r="C35" t="s">
+        <v>475</v>
+      </c>
+      <c r="D35" t="s">
+        <v>487</v>
+      </c>
+      <c r="E35" t="s">
+        <v>483</v>
+      </c>
+      <c r="F35" t="s">
+        <v>478</v>
+      </c>
+      <c r="G35">
+        <v>12</v>
+      </c>
+      <c r="H35">
+        <v>1500</v>
+      </c>
+      <c r="I35">
+        <v>18000</v>
+      </c>
+      <c r="J35" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>521</v>
+      </c>
+      <c r="B36" s="52">
+        <v>46061</v>
+      </c>
+      <c r="C36" t="s">
+        <v>481</v>
+      </c>
+      <c r="D36" t="s">
+        <v>470</v>
+      </c>
+      <c r="E36" t="s">
+        <v>490</v>
+      </c>
+      <c r="F36" t="s">
+        <v>472</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>18000</v>
+      </c>
+      <c r="I36">
+        <v>54000</v>
+      </c>
+      <c r="J36" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>522</v>
+      </c>
+      <c r="B37" s="52">
+        <v>46062</v>
+      </c>
+      <c r="C37" t="s">
+        <v>486</v>
+      </c>
+      <c r="D37" t="s">
+        <v>476</v>
+      </c>
+      <c r="E37" t="s">
+        <v>492</v>
+      </c>
+      <c r="F37" t="s">
+        <v>478</v>
+      </c>
+      <c r="G37">
+        <v>7</v>
+      </c>
+      <c r="H37">
+        <v>2500</v>
+      </c>
+      <c r="I37">
+        <v>17500</v>
+      </c>
+      <c r="J37" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>523</v>
+      </c>
+      <c r="B38" s="52">
+        <v>46063</v>
+      </c>
+      <c r="C38" t="s">
+        <v>469</v>
+      </c>
+      <c r="D38" t="s">
+        <v>476</v>
+      </c>
+      <c r="E38" t="s">
+        <v>471</v>
+      </c>
+      <c r="F38" t="s">
+        <v>472</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>55000</v>
+      </c>
+      <c r="I38">
+        <v>110000</v>
+      </c>
+      <c r="J38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>524</v>
+      </c>
+      <c r="B39" s="52">
+        <v>46064</v>
+      </c>
+      <c r="C39" t="s">
+        <v>475</v>
+      </c>
+      <c r="D39" t="s">
+        <v>482</v>
+      </c>
+      <c r="E39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F39" t="s">
+        <v>478</v>
+      </c>
+      <c r="G39">
+        <v>30</v>
+      </c>
+      <c r="H39">
+        <v>800</v>
+      </c>
+      <c r="I39">
+        <v>24000</v>
+      </c>
+      <c r="J39" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>525</v>
+      </c>
+      <c r="B40" s="52">
+        <v>46065</v>
+      </c>
+      <c r="C40" t="s">
+        <v>481</v>
+      </c>
+      <c r="D40" t="s">
+        <v>487</v>
+      </c>
+      <c r="E40" t="s">
+        <v>488</v>
+      </c>
+      <c r="F40" t="s">
+        <v>472</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>12000</v>
+      </c>
+      <c r="I40">
+        <v>48000</v>
+      </c>
+      <c r="J40" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>526</v>
+      </c>
+      <c r="B41" s="52">
+        <v>46066</v>
+      </c>
+      <c r="C41" t="s">
+        <v>486</v>
+      </c>
+      <c r="D41" t="s">
+        <v>470</v>
+      </c>
+      <c r="E41" t="s">
+        <v>483</v>
+      </c>
+      <c r="F41" t="s">
+        <v>478</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41">
+        <v>1500</v>
+      </c>
+      <c r="I41">
+        <v>22500</v>
+      </c>
+      <c r="J41" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>527</v>
+      </c>
+      <c r="B42" s="52">
+        <v>46067</v>
+      </c>
+      <c r="C42" t="s">
+        <v>469</v>
+      </c>
+      <c r="D42" t="s">
+        <v>470</v>
+      </c>
+      <c r="E42" t="s">
+        <v>490</v>
+      </c>
+      <c r="F42" t="s">
+        <v>472</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42">
+        <v>18000</v>
+      </c>
+      <c r="I42">
+        <v>36000</v>
+      </c>
+      <c r="J42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>528</v>
+      </c>
+      <c r="B43" s="52">
+        <v>46068</v>
+      </c>
+      <c r="C43" t="s">
+        <v>475</v>
+      </c>
+      <c r="D43" t="s">
+        <v>476</v>
+      </c>
+      <c r="E43" t="s">
+        <v>492</v>
+      </c>
+      <c r="F43" t="s">
+        <v>478</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>2500</v>
+      </c>
+      <c r="I43">
+        <v>25000</v>
+      </c>
+      <c r="J43" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>529</v>
+      </c>
+      <c r="B44" s="52">
+        <v>46069</v>
+      </c>
+      <c r="C44" t="s">
+        <v>481</v>
+      </c>
+      <c r="D44" t="s">
+        <v>482</v>
+      </c>
+      <c r="E44" t="s">
+        <v>471</v>
+      </c>
+      <c r="F44" t="s">
+        <v>472</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+      <c r="H44">
+        <v>55000</v>
+      </c>
+      <c r="I44">
+        <v>165000</v>
+      </c>
+      <c r="J44" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>530</v>
+      </c>
+      <c r="B45" s="52">
+        <v>46070</v>
+      </c>
+      <c r="C45" t="s">
+        <v>486</v>
+      </c>
+      <c r="D45" t="s">
+        <v>487</v>
+      </c>
+      <c r="E45" t="s">
+        <v>477</v>
+      </c>
+      <c r="F45" t="s">
+        <v>478</v>
+      </c>
+      <c r="G45">
+        <v>22</v>
+      </c>
+      <c r="H45">
+        <v>800</v>
+      </c>
+      <c r="I45">
+        <v>17600</v>
+      </c>
+      <c r="J45" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>531</v>
+      </c>
+      <c r="B46" s="52">
+        <v>46071</v>
+      </c>
+      <c r="C46" t="s">
+        <v>469</v>
+      </c>
+      <c r="D46" t="s">
+        <v>482</v>
+      </c>
+      <c r="E46" t="s">
+        <v>488</v>
+      </c>
+      <c r="F46" t="s">
+        <v>472</v>
+      </c>
+      <c r="G46">
         <v>5</v>
       </c>
-      <c r="D16">
+      <c r="H46">
+        <v>12000</v>
+      </c>
+      <c r="I46">
+        <v>60000</v>
+      </c>
+      <c r="J46" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>532</v>
+      </c>
+      <c r="B47" s="52">
+        <v>46072</v>
+      </c>
+      <c r="C47" t="s">
+        <v>475</v>
+      </c>
+      <c r="D47" t="s">
+        <v>470</v>
+      </c>
+      <c r="E47" t="s">
+        <v>483</v>
+      </c>
+      <c r="F47" t="s">
+        <v>478</v>
+      </c>
+      <c r="G47">
+        <v>11</v>
+      </c>
+      <c r="H47">
+        <v>1500</v>
+      </c>
+      <c r="I47">
+        <v>16500</v>
+      </c>
+      <c r="J47" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>533</v>
+      </c>
+      <c r="B48" s="52">
+        <v>46073</v>
+      </c>
+      <c r="C48" t="s">
+        <v>481</v>
+      </c>
+      <c r="D48" t="s">
+        <v>476</v>
+      </c>
+      <c r="E48" t="s">
+        <v>490</v>
+      </c>
+      <c r="F48" t="s">
+        <v>472</v>
+      </c>
+      <c r="G48">
         <v>2</v>
+      </c>
+      <c r="H48">
+        <v>18000</v>
+      </c>
+      <c r="I48">
+        <v>36000</v>
+      </c>
+      <c r="J48" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>534</v>
+      </c>
+      <c r="B49" s="52">
+        <v>46074</v>
+      </c>
+      <c r="C49" t="s">
+        <v>486</v>
+      </c>
+      <c r="D49" t="s">
+        <v>487</v>
+      </c>
+      <c r="E49" t="s">
+        <v>492</v>
+      </c>
+      <c r="F49" t="s">
+        <v>478</v>
+      </c>
+      <c r="G49">
+        <v>9</v>
+      </c>
+      <c r="H49">
+        <v>2500</v>
+      </c>
+      <c r="I49">
+        <v>22500</v>
+      </c>
+      <c r="J49" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>535</v>
+      </c>
+      <c r="B50" s="52">
+        <v>46075</v>
+      </c>
+      <c r="C50" t="s">
+        <v>469</v>
+      </c>
+      <c r="D50" t="s">
+        <v>487</v>
+      </c>
+      <c r="E50" t="s">
+        <v>471</v>
+      </c>
+      <c r="F50" t="s">
+        <v>472</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50">
+        <v>55000</v>
+      </c>
+      <c r="I50">
+        <v>110000</v>
+      </c>
+      <c r="J50" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>536</v>
+      </c>
+      <c r="B51" s="52">
+        <v>46076</v>
+      </c>
+      <c r="C51" t="s">
+        <v>475</v>
+      </c>
+      <c r="D51" t="s">
+        <v>482</v>
+      </c>
+      <c r="E51" t="s">
+        <v>477</v>
+      </c>
+      <c r="F51" t="s">
+        <v>478</v>
+      </c>
+      <c r="G51">
+        <v>28</v>
+      </c>
+      <c r="H51">
+        <v>800</v>
+      </c>
+      <c r="I51">
+        <v>22400</v>
+      </c>
+      <c r="J51" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -4963,19 +10127,99 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15">
+      <c r="A2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15">
+      <c r="A3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15">
+      <c r="D4" s="36" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15">
+      <c r="D5" s="36" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15">
+      <c r="D6" s="36" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15">
+      <c r="D7" s="36" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15">
+      <c r="D8" s="36" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15">
+      <c r="D9" s="36" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15">
+      <c r="D10" s="36" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15">
+      <c r="D11" s="36" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3073DD66-6F87-4BE6-9313-9EA867561D3B}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -4986,158 +10230,158 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FB00EB-1F40-48CD-BEDF-7ACFFA4D03F4}">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="14" customWidth="1"/>
     <col min="2" max="2" width="43.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" customWidth="1"/>
     <col min="6" max="6" width="17.6328125" customWidth="1"/>
     <col min="10" max="10" width="17.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15">
-      <c r="A1" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1" s="16"/>
+      <c r="A1" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="25" t="str">
+      <c r="A2" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="24" t="str">
         <f>LEFT(A2,3)</f>
         <v>+91</v>
       </c>
-      <c r="C2" s="25" t="str">
+      <c r="C2" s="24" t="str">
         <f>RIGHT(A2,10)</f>
         <v>8989889989</v>
       </c>
       <c r="F2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="B3" s="25" t="str">
+      <c r="A3" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B3" s="24" t="str">
         <f t="shared" ref="B3:B7" si="0">LEFT(A3,3)</f>
         <v>+91</v>
       </c>
-      <c r="C3" s="25" t="str">
+      <c r="C3" s="24" t="str">
         <f t="shared" ref="C3:C7" si="1">RIGHT(A3,10)</f>
         <v>8989889989</v>
       </c>
       <c r="F3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="B4" s="25" t="str">
+      <c r="A4" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="24" t="str">
         <f t="shared" si="0"/>
         <v>+91</v>
       </c>
-      <c r="C4" s="25" t="str">
+      <c r="C4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>8989889989</v>
       </c>
       <c r="F4" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
-      <c r="A5" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="B5" s="25" t="str">
+      <c r="A5" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="24" t="str">
         <f t="shared" si="0"/>
         <v>+91</v>
       </c>
-      <c r="C5" s="25" t="str">
+      <c r="C5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>8989889989</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="25" t="str">
+      <c r="A6" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="24" t="str">
         <f t="shared" si="0"/>
         <v>+91</v>
       </c>
-      <c r="C6" s="25" t="str">
+      <c r="C6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>8989889989</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="B7" s="25" t="str">
+      <c r="A7" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="24" t="str">
         <f t="shared" si="0"/>
         <v>+91</v>
       </c>
-      <c r="C7" s="25" t="str">
+      <c r="C7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>8989889989</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="22"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
     </row>
     <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
+      <c r="A9" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="25" t="str">
+      <c r="A10" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="24" t="str">
         <f>MID(A10,5,1)</f>
         <v>E</v>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="24"/>
     </row>
     <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="B11" s="25" t="str">
+      <c r="A11" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="24" t="str">
         <f>MID(A11,5,2)</f>
         <v>SS</v>
       </c>
-      <c r="C11" s="25"/>
+      <c r="C11" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="15">
-      <c r="A13" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="D13" s="26" t="str">
+      <c r="A13" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="25" t="str">
         <f>_xlfn.TEXTBEFORE(C13," ",)</f>
         <v>Sundar</v>
       </c>
@@ -5147,42 +10391,42 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26" t="str">
+      <c r="A14" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25" t="str">
         <f>_xlfn.TEXTAFTER(C13," ",)</f>
         <v>Lingam</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="28"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
+      <c r="A16" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="36" t="s">
-        <v>279</v>
-      </c>
-      <c r="B17" s="26" t="str">
+      <c r="A17" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="25" t="str">
         <f>_xlfn.TEXTAFTER(B16," ")</f>
         <v>Lingam Chennai</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
       <c r="F17" t="str">
         <f>_xlfn.TEXTAFTER(B16," ")</f>
         <v>Lingam Chennai</v>
@@ -5193,50 +10437,50 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B18" s="26" t="str">
+      <c r="A18" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" s="25" t="str">
         <f>_xlfn.TEXTAFTER(B16," ",2)</f>
         <v>Chennai</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="36" t="s">
-        <v>281</v>
-      </c>
-      <c r="B19" s="26" t="e">
+      <c r="A19" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="B19" s="25" t="e">
         <f>_xlfn.TEXTAFTER(B16,",")</f>
         <v>#N/A</v>
       </c>
-      <c r="C19" s="26" t="str">
+      <c r="C19" s="25" t="str">
         <f>_xlfn.TEXTAFTER(B16,",",,,,"no")</f>
         <v>no</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="25"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="34" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
+      <c r="A21" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="B22" s="20" t="str" cm="1">
+      <c r="A22" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B22" s="19" t="str" cm="1">
         <f t="array" ref="B22:D22">_xlfn.TEXTSPLIT(A22,",")</f>
         <v>Data science</v>
       </c>
-      <c r="C22" s="20" t="str">
+      <c r="C22" s="19" t="str">
         <v>python</v>
       </c>
-      <c r="D22" s="20" t="str">
+      <c r="D22" s="19" t="str">
         <v>django</v>
       </c>
       <c r="F22" t="str" cm="1">
@@ -5251,52 +10495,52 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="B23" s="20" t="str" cm="1">
+      <c r="A23" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" s="19" t="str" cm="1">
         <f t="array" ref="B23">_xlfn.TEXTSPLIT(A23,",")</f>
         <v>Data science</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
       <c r="F23" t="str" cm="1">
         <f t="array" ref="F23">_xlfn.TEXTSPLIT(A23,",")</f>
         <v>Data science</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="21"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="21"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
     </row>
     <row r="26" spans="1:10" ht="15">
-      <c r="A26" s="34" t="s">
-        <v>285</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
+      <c r="A26" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
     </row>
     <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="B27" s="20" t="str" cm="1">
+      <c r="A27" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B27" s="19" t="str" cm="1">
         <f t="array" ref="B27:D29">_xlfn.TEXTSPLIT(A27,",","|")</f>
         <v>Data science</v>
       </c>
-      <c r="C27" s="20" t="str">
+      <c r="C27" s="19" t="str">
         <v>python</v>
       </c>
-      <c r="D27" s="20" t="str">
+      <c r="D27" s="19" t="str">
         <v>django</v>
       </c>
       <c r="F27" t="str" cm="1">
@@ -5315,14 +10559,14 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="21"/>
-      <c r="B28" s="20" t="str">
+      <c r="A28" s="20"/>
+      <c r="B28" s="19" t="str">
         <v xml:space="preserve">SQL </v>
       </c>
-      <c r="C28" s="20" t="str">
+      <c r="C28" s="19" t="str">
         <v>postgress</v>
       </c>
-      <c r="D28" s="20" t="e">
+      <c r="D28" s="19" t="e">
         <v>#N/A</v>
       </c>
       <c r="F28" t="str">
@@ -5339,14 +10583,14 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="21"/>
-      <c r="B29" s="20" t="str">
+      <c r="A29" s="20"/>
+      <c r="B29" s="19" t="str">
         <v>pandas</v>
       </c>
-      <c r="C29" s="20" t="str">
+      <c r="C29" s="19" t="str">
         <v>seaborn</v>
       </c>
-      <c r="D29" s="20" t="e">
+      <c r="D29" s="19" t="e">
         <v>#N/A</v>
       </c>
       <c r="F29" t="str">
@@ -5363,143 +10607,143 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-    </row>
-    <row r="33" spans="1:8" ht="15">
-      <c r="A33" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="B33" s="18" t="str" cm="1">
+      <c r="A32" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+    </row>
+    <row r="33" spans="1:10" ht="15">
+      <c r="A33" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" s="17" t="str" cm="1">
         <f t="array" ref="B33:E33">_xlfn.TEXTSPLIT(A33,",")</f>
         <v>Data science</v>
       </c>
-      <c r="C33" s="18" t="str">
+      <c r="C33" s="17" t="str">
         <v/>
       </c>
-      <c r="D33" s="18" t="str">
+      <c r="D33" s="17" t="str">
         <v>python</v>
       </c>
-      <c r="E33" s="18" t="str">
+      <c r="E33" s="17" t="str">
         <v>django</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15">
-      <c r="A34" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="B34" s="18" t="str" cm="1">
+    <row r="34" spans="1:10" ht="15">
+      <c r="A34" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" s="17" t="str" cm="1">
         <f t="array" ref="B34:D34">_xlfn.TEXTSPLIT(A34,",",,TRUE)</f>
         <v>Data science</v>
       </c>
-      <c r="C34" s="18" t="str">
+      <c r="C34" s="17" t="str">
         <v>python</v>
       </c>
-      <c r="D34" s="18" t="str">
+      <c r="D34" s="17" t="str">
         <v>django</v>
       </c>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="37" spans="1:8" ht="15">
-      <c r="A37" s="29" t="s">
+      <c r="E34" s="17"/>
+    </row>
+    <row r="37" spans="1:10" ht="15">
+      <c r="A37" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+    </row>
+    <row r="38" spans="1:10" ht="15">
+      <c r="A38" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+    </row>
+    <row r="39" spans="1:10" ht="15">
+      <c r="A39" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+    </row>
+    <row r="40" spans="1:10" ht="15">
+      <c r="A40" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="32"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+    </row>
+    <row r="42" spans="1:10" ht="15">
+      <c r="A42" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-    </row>
-    <row r="38" spans="1:8" ht="15">
-      <c r="A38" s="31" t="s">
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+    </row>
+    <row r="43" spans="1:10" ht="15">
+      <c r="A43" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B43" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="E43" s="31" t="s">
         <v>291</v>
-      </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-    </row>
-    <row r="39" spans="1:8" ht="15">
-      <c r="A39" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="B39" s="32" t="s">
-        <v>292</v>
-      </c>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-    </row>
-    <row r="40" spans="1:8" ht="15">
-      <c r="A40" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="B40" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="33"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-    </row>
-    <row r="42" spans="1:8" ht="15">
-      <c r="A42" s="31" t="s">
-        <v>294</v>
-      </c>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-    </row>
-    <row r="43" spans="1:8" ht="15">
-      <c r="A43" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="B43" s="32" t="s">
-        <v>296</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="E43" s="32" t="s">
-        <v>297</v>
       </c>
       <c r="F43">
         <f>FIND(A44,B44)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15">
-      <c r="A44" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="B44" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="C44" s="30">
+    <row r="44" spans="1:10" ht="15">
+      <c r="A44" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" s="29">
         <f>FIND(A44,B44)</f>
         <v>11</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="29">
         <f>SEARCH(A44,B44)</f>
         <v>11</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="29">
         <f>LEN(B44)</f>
         <v>44</v>
       </c>
@@ -5508,164 +10752,960 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15">
-      <c r="A45" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="C45" s="30" t="e">
+    <row r="45" spans="1:10" ht="15">
+      <c r="A45" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="C45" s="29" t="e">
         <f>FIND(A45,B45)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="29">
         <f>SEARCH(A45,B45)</f>
         <v>11</v>
       </c>
-      <c r="E45" s="30">
+      <c r="E45" s="29">
         <f>LEN(B45)</f>
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15">
-      <c r="A46" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="B46" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="C46" s="30">
+    <row r="46" spans="1:10" ht="15">
+      <c r="A46" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C46" s="29">
         <f>FIND(A46,B46)</f>
         <v>33</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="29">
         <f>SEARCH(A46,B46)</f>
         <v>1</v>
       </c>
-      <c r="E46" s="30"/>
-    </row>
-    <row r="47" spans="1:8" ht="15">
-      <c r="B47" s="16"/>
-    </row>
-    <row r="48" spans="1:8" ht="15">
-      <c r="A48" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="F48" t="str">
+      <c r="E46" s="29"/>
+    </row>
+    <row r="47" spans="1:10" ht="15">
+      <c r="B47" s="15"/>
+    </row>
+    <row r="48" spans="1:10" ht="15">
+      <c r="A48" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="B48" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F48" s="44" t="str">
         <f>CONCATENATE(D48," ",E48,D48)</f>
         <v>Sundar LingamSundar</v>
       </c>
-      <c r="H48" t="str">
+      <c r="G48" s="44"/>
+      <c r="H48" s="44" t="str">
         <f>CONCATENATE(D48," ",E48,F48,B48)</f>
         <v>Sundar LingamSundar LingamSundarConcatenate</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="15">
-      <c r="A49" s="15" t="s">
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+    </row>
+    <row r="49" spans="1:10" ht="15">
+      <c r="A49" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="B49" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>305</v>
+      </c>
+      <c r="D49" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="B49" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="F49" t="str">
+      <c r="E49" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F49" s="44" t="str">
         <f>_xlfn.CONCAT(D49," ",E49)</f>
         <v>Sundar Lingam</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="15">
-      <c r="A50" s="15" t="s">
+      <c r="G49" s="44"/>
+      <c r="H49" s="44" t="str">
+        <f>_xlfn.CONCAT(D49:F49)</f>
+        <v>SundarLingamSundar Lingam</v>
+      </c>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+    </row>
+    <row r="50" spans="1:10" ht="15">
+      <c r="A50" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="C50" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="D50" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="E50" s="43" t="s">
         <v>309</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="F50" t="str">
+      <c r="F50" s="44" t="str">
         <f>_xlfn.TEXTJOIN(" ",TRUE,E50,D50)</f>
         <v>Lingam Sundar</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="15">
-      <c r="A51" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="F51" t="str">
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+    </row>
+    <row r="51" spans="1:10" ht="15">
+      <c r="A51" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="C51" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="D51" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F51" s="44" t="str">
         <f>D51&amp;E51</f>
         <v>SundarLingam</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G51" s="44" t="str">
         <f>E51&amp;" "&amp;D51</f>
         <v>Lingam Sundar</v>
       </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="C53" t="str">
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="46"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="46"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44" t="str">
         <f>CONCATENATE(D48," ",E48)</f>
         <v>Sundar Lingam</v>
       </c>
-      <c r="E53" t="str">
+      <c r="D53" s="44"/>
+      <c r="E53" s="44" t="str">
         <f>CONCATENATE(E48," ",D48)</f>
         <v>Lingam Sundar</v>
       </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="C54" t="str">
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="46"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44" t="str">
         <f>_xlfn.CONCAT(D48,E48)</f>
         <v>SundarLingam</v>
       </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="C55" t="str">
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="46"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44" t="str">
         <f>_xlfn.TEXTJOIN(" ",TRUE,D48,E48)</f>
         <v>Sundar Lingam</v>
       </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="C56" t="str">
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="46"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44" t="str">
         <f>D51&amp;E51</f>
         <v>SundarLingam</v>
+      </c>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
+    </row>
+    <row r="58" spans="1:10" ht="15">
+      <c r="A58" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="B58" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,A57:A65)</f>
+        <v>Helo I am Sundhar Lingam Also called  sundar</v>
+      </c>
+      <c r="C58" s="47" t="s">
+        <v>322</v>
+      </c>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+    </row>
+    <row r="59" spans="1:10" ht="15">
+      <c r="A59" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="B59" s="46" t="str">
+        <f>A57&amp;A58&amp;A59</f>
+        <v>HeloIam</v>
+      </c>
+      <c r="C59" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="44"/>
+      <c r="J59" s="44"/>
+    </row>
+    <row r="60" spans="1:10" ht="15">
+      <c r="A60" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="B60" s="44"/>
+      <c r="C60" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="D60" s="47" t="s">
+        <v>326</v>
+      </c>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
+    </row>
+    <row r="61" spans="1:10" ht="15">
+      <c r="A61" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="B61" s="44"/>
+      <c r="C61" s="47" t="s">
+        <v>325</v>
+      </c>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="44"/>
+      <c r="J61" s="44"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="46"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="44"/>
+      <c r="J62" s="44"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
+      <c r="J63" s="44"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="44"/>
+      <c r="J64" s="44"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
+    </row>
+    <row r="67" spans="1:10" ht="15">
+      <c r="A67" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="B67" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="C67" s="40" t="str">
+        <f>UPPER(B67)</f>
+        <v>BELIEVE YOU CAN AND YOU ARE HALFWAY THERE</v>
+      </c>
+      <c r="D67" s="40"/>
+      <c r="E67" s="41" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="15">
+      <c r="A68" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="B68" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="C68" s="40" t="str">
+        <f>LOWER(B68)</f>
+        <v>they key to success is to focus to the goal you want to achieve in you life, not the obstacles</v>
+      </c>
+      <c r="D68" s="40"/>
+      <c r="E68" s="41" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="15">
+      <c r="A69" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="B69" s="39" t="s">
+        <v>332</v>
+      </c>
+      <c r="C69" s="40" t="str">
+        <f>PROPER(B69)</f>
+        <v>Focus On The Goal</v>
+      </c>
+      <c r="D69" s="40"/>
+      <c r="E69" s="41" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" s="49" customFormat="1" ht="15">
+      <c r="A71" s="48" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="49" customFormat="1" ht="15">
+      <c r="A72" s="48" t="s">
+        <v>337</v>
+      </c>
+      <c r="B72" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="C72" s="49" t="s">
+        <v>330</v>
+      </c>
+      <c r="D72" s="49" t="str">
+        <f>REPLACE(C72,9,3,"u")</f>
+        <v>Believe u can and you are halfway there</v>
+      </c>
+      <c r="F72" s="51" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="49" customFormat="1" ht="15">
+      <c r="A73" s="48" t="s">
+        <v>338</v>
+      </c>
+      <c r="B73" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="C73" s="49" t="str">
+        <f>SUBSTITUTE(C72,"you","u",1)</f>
+        <v>Believe u can and you are halfway there</v>
+      </c>
+      <c r="F73" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="H73" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="I73" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="J73" s="49" t="str">
+        <f>SUBSTITUTE(H73,"php","python",2)</f>
+        <v>php,java,python</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="15">
+      <c r="F76" s="37" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E42D0720-D89C-49FE-A48B-A8BA7AD95A9A}">
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6328125" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="7" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="54" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="57"/>
+    </row>
+    <row r="2" spans="1:10" ht="15">
+      <c r="A2" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2" s="61">
+        <f>DATE(2026,9,25)</f>
+        <v>46290</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="52">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
+      <c r="A3" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>364</v>
+      </c>
+      <c r="D3" s="64">
+        <f>TIME(6,9,15)</f>
+        <v>0.25642361111111112</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>359</v>
+      </c>
+      <c r="F3" s="64">
+        <f>TIME(21,20,10)</f>
+        <v>0.88900462962962967</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>360</v>
+      </c>
+      <c r="H3" s="64"/>
+      <c r="I3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="61">
+        <f>DATE(2026,9,1)+TIME(1,45,34)</f>
+        <v>46266.073310185187</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
+    </row>
+    <row r="5" spans="1:10" ht="15">
+      <c r="A5" s="58" t="s">
+        <v>350</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>365</v>
+      </c>
+      <c r="D5" s="61">
+        <f ca="1">TODAY()</f>
+        <v>46290</v>
+      </c>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
+    </row>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="65" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>356</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>366</v>
+      </c>
+      <c r="D6" s="68">
+        <f ca="1">NOW()</f>
+        <v>46290.525716203701</v>
+      </c>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+    </row>
+    <row r="8" spans="1:10" ht="15">
+      <c r="A8" s="36" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" s="72">
+        <v>44996</v>
+      </c>
+      <c r="D10" t="e">
+        <f>DATEVALUE(C10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
+      <c r="A11" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="C11" s="71">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D11" t="e">
+        <f>TIMEVALUE(C11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" s="53">
+        <f>MIN(C11)</f>
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
+      <c r="A13" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="72">
+        <v>44996</v>
+      </c>
+      <c r="D13">
+        <f>DAY(C13)</f>
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <f>DAY(C13)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
+      <c r="B14" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14">
+        <f>MONTH(C13)</f>
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <f>MONTH(C13)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="B15" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="D15" s="37">
+        <f>YEAR(C13)</f>
+        <v>2023</v>
+      </c>
+      <c r="H15">
+        <f>YEAR(C13)</f>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
+      <c r="B16" s="36" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15">
+      <c r="B17" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17">
+        <f>WEEKNUM(C13,1)</f>
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <f>WEEKDAY(C10,2)</f>
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <f>WEEKDAY(C13,2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15">
+      <c r="B18" s="36" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15">
+      <c r="B19" s="36" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15">
+      <c r="B20" s="36" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="C22" s="78" t="s">
+        <v>554</v>
+      </c>
+      <c r="D22" s="78" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15">
+      <c r="A23" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="C23" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D23" s="79">
+        <v>46675</v>
+      </c>
+      <c r="E23">
+        <f>DATEDIF(C23,D23,"Y")</f>
+        <v>1</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="J23">
+        <f>DATEDIF(C23,D23,"d")</f>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15">
+      <c r="A24" s="36"/>
+      <c r="B24" s="37" t="s">
+        <v>383</v>
+      </c>
+      <c r="C24" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D24" s="79">
+        <v>46371</v>
+      </c>
+      <c r="E24">
+        <f>DATEDIF(C24,D24,"m")</f>
+        <v>2</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15">
+      <c r="A25" s="36"/>
+      <c r="B25" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="C25" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D25" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E25">
+        <f>DATEDIF(C25,D25,"d")</f>
+        <v>20</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15">
+      <c r="A26" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="C26" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D26" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E26">
+        <f>_xlfn.DAYS(D26,C26)</f>
+        <v>20</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15">
+      <c r="A27" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="C27" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D27" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E27">
+        <f>NETWORKDAYS(C27,D27)</f>
+        <v>15</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15">
+      <c r="A28" s="36"/>
+      <c r="B28" s="37" t="s">
+        <v>389</v>
+      </c>
+      <c r="C28" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D28" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E28">
+        <f>NETWORKDAYS.INTL(C28,D28,11)</f>
+        <v>18</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15">
+      <c r="A29" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="C29" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D29" s="79">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15">
+      <c r="A30" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="C30" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D30" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E30">
+        <f>YEARFRAC(C30,D30)</f>
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15">
+      <c r="A32" s="37" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15">
+      <c r="A33" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>403</v>
+      </c>
+      <c r="C33" s="52">
+        <v>46290</v>
+      </c>
+      <c r="D33" s="52">
+        <f>EDATE(C33,3)</f>
+        <v>46381</v>
+      </c>
+      <c r="E33" s="52">
+        <f>EDATE(D33,-3)</f>
+        <v>46290</v>
+      </c>
+      <c r="G33" s="52">
+        <f>EDATE(C33,5)</f>
+        <v>46443</v>
+      </c>
+      <c r="H33" s="52">
+        <f>EDATE(C33,-5)</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>402</v>
+      </c>
+      <c r="C34" s="52">
+        <f>EOMONTH(C33,3)</f>
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="B35" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35">
+        <f>WORKDAY(C33,5)</f>
+        <v>46297</v>
       </c>
     </row>
   </sheetData>

--- a/excel/sample.xlsx
+++ b/excel/sample.xlsx
@@ -8,25 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skillfort\SkillFortClass\DataAnalytics03\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C2568C-3150-4582-9535-C895F355E4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9952D6-8625-4096-BC0D-496EBC524DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rawdata" sheetId="1" r:id="rId1"/>
     <sheet name="lookup" sheetId="3" r:id="rId2"/>
     <sheet name="index and match" sheetId="7" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="10" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId4"/>
     <sheet name="Pivot" sheetId="8" r:id="rId5"/>
-    <sheet name="filter" sheetId="2" r:id="rId6"/>
-    <sheet name="link" sheetId="4" r:id="rId7"/>
-    <sheet name="text" sheetId="5" r:id="rId8"/>
-    <sheet name="datetime" sheetId="6" r:id="rId9"/>
+    <sheet name="data validation" sheetId="12" r:id="rId6"/>
+    <sheet name="filter" sheetId="2" r:id="rId7"/>
+    <sheet name="link" sheetId="4" r:id="rId8"/>
+    <sheet name="text" sheetId="5" r:id="rId9"/>
+    <sheet name="datetime" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rawdata!$A$1:$G$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="33" r:id="rId11"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -47,7 +51,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -69,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="568">
   <si>
     <t>ID</t>
   </si>
@@ -1832,6 +1836,39 @@
   <si>
     <t>withlock</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Revenue</t>
+  </si>
+  <si>
+    <t>Count of Order_ID</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Fees</t>
+  </si>
 </sst>
 </file>
 
@@ -1840,12 +1877,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2099,113 +2143,123 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="18" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="18" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="18" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2231,6 +2285,2481 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[sample.xlsx]Sheet1!PivotTable13</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent2">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent2">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent2">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent2">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$28:$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Karthik</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$30:$A$34</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="2"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Printer</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Monitor</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>North</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>West</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$30:$B$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>144000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>84000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-28F1-46E3-9938-EA6D1F810834}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="315"/>
+        <c:overlap val="-40"/>
+        <c:axId val="1978812288"/>
+        <c:axId val="1978810368"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1978812288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Pr</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>oduct</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.51201027996500437"/>
+              <c:y val="0.79738626421697301"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1978810368"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1978810368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>revenue</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1978812288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>288925</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>593725</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{720B5E7A-DF1D-4139-DA14-9A1F52C477D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="DELL" refreshedDate="46291.50860833333" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{60CFB5B2-461C-4036-8BD4-ED29DD8DF7BB}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:J51" sheet="Pivot"/>
+  </cacheSource>
+  <cacheFields count="10">
+    <cacheField name="Order_ID" numFmtId="0">
+      <sharedItems count="50">
+        <s v="ORD001"/>
+        <s v="ORD002"/>
+        <s v="ORD003"/>
+        <s v="ORD004"/>
+        <s v="ORD005"/>
+        <s v="ORD006"/>
+        <s v="ORD007"/>
+        <s v="ORD008"/>
+        <s v="ORD009"/>
+        <s v="ORD010"/>
+        <s v="ORD011"/>
+        <s v="ORD012"/>
+        <s v="ORD013"/>
+        <s v="ORD014"/>
+        <s v="ORD015"/>
+        <s v="ORD016"/>
+        <s v="ORD017"/>
+        <s v="ORD018"/>
+        <s v="ORD019"/>
+        <s v="ORD020"/>
+        <s v="ORD021"/>
+        <s v="ORD022"/>
+        <s v="ORD023"/>
+        <s v="ORD024"/>
+        <s v="ORD025"/>
+        <s v="ORD026"/>
+        <s v="ORD027"/>
+        <s v="ORD028"/>
+        <s v="ORD029"/>
+        <s v="ORD030"/>
+        <s v="ORD031"/>
+        <s v="ORD032"/>
+        <s v="ORD033"/>
+        <s v="ORD034"/>
+        <s v="ORD035"/>
+        <s v="ORD036"/>
+        <s v="ORD037"/>
+        <s v="ORD038"/>
+        <s v="ORD039"/>
+        <s v="ORD040"/>
+        <s v="ORD041"/>
+        <s v="ORD042"/>
+        <s v="ORD043"/>
+        <s v="ORD044"/>
+        <s v="ORD045"/>
+        <s v="ORD046"/>
+        <s v="ORD047"/>
+        <s v="ORD048"/>
+        <s v="ORD049"/>
+        <s v="ORD050"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-05T00:00:00" maxDate="2026-02-24T00:00:00"/>
+    </cacheField>
+    <cacheField name="Salesperson" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Arun"/>
+        <s v="Priya"/>
+        <s v="Karthik"/>
+        <s v="Divya"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="North"/>
+        <s v="South"/>
+        <s v="East"/>
+        <s v="West"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Laptop"/>
+        <s v="Mouse"/>
+        <s v="Keyboard"/>
+        <s v="Monitor"/>
+        <s v="Printer"/>
+        <s v="Headset"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="30"/>
+    </cacheField>
+    <cacheField name="Unit_Price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="800" maxValue="55000"/>
+    </cacheField>
+    <cacheField name="Revenue" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="7500" maxValue="165000"/>
+    </cacheField>
+    <cacheField name="Payment_Mode" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+  <r>
+    <x v="0"/>
+    <d v="2026-01-05T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="55000"/>
+    <n v="110000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <d v="2026-01-06T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="10"/>
+    <n v="800"/>
+    <n v="8000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <d v="2026-01-07T00:00:00"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="5"/>
+    <n v="1500"/>
+    <n v="7500"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <d v="2026-01-08T00:00:00"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="3"/>
+    <n v="12000"/>
+    <n v="36000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <d v="2026-01-09T00:00:00"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="18000"/>
+    <n v="36000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <d v="2026-01-10T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="8"/>
+    <n v="2500"/>
+    <n v="20000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <d v="2026-01-11T00:00:00"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="1"/>
+    <n v="55000"/>
+    <n v="55000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <d v="2026-01-12T00:00:00"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="15"/>
+    <n v="800"/>
+    <n v="12000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <d v="2026-01-13T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="4"/>
+    <n v="12000"/>
+    <n v="48000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <d v="2026-01-14T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="7"/>
+    <n v="1500"/>
+    <n v="10500"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <d v="2026-01-15T00:00:00"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="3"/>
+    <n v="18000"/>
+    <n v="54000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <d v="2026-01-16T00:00:00"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="6"/>
+    <n v="2500"/>
+    <n v="15000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <d v="2026-01-17T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="3"/>
+    <n v="55000"/>
+    <n v="165000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <d v="2026-01-18T00:00:00"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="20"/>
+    <n v="800"/>
+    <n v="16000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <d v="2026-01-19T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="12000"/>
+    <n v="24000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <d v="2026-01-20T00:00:00"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="10"/>
+    <n v="1500"/>
+    <n v="15000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <d v="2026-01-21T00:00:00"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="1"/>
+    <n v="18000"/>
+    <n v="18000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <d v="2026-01-22T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="12"/>
+    <n v="2500"/>
+    <n v="30000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <d v="2026-01-23T00:00:00"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="55000"/>
+    <n v="110000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <d v="2026-01-24T00:00:00"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="18"/>
+    <n v="800"/>
+    <n v="14400"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <d v="2026-01-25T00:00:00"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="5"/>
+    <n v="12000"/>
+    <n v="60000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <d v="2026-01-26T00:00:00"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="9"/>
+    <n v="1500"/>
+    <n v="13500"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <d v="2026-01-27T00:00:00"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="18000"/>
+    <n v="36000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <d v="2026-01-28T00:00:00"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="10"/>
+    <n v="2500"/>
+    <n v="25000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <d v="2026-01-29T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="1"/>
+    <n v="55000"/>
+    <n v="55000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <d v="2026-01-30T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="25"/>
+    <n v="800"/>
+    <n v="20000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <d v="2026-01-31T00:00:00"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="3"/>
+    <n v="12000"/>
+    <n v="36000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <d v="2026-02-01T00:00:00"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="8"/>
+    <n v="1500"/>
+    <n v="12000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <d v="2026-02-02T00:00:00"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="4"/>
+    <n v="18000"/>
+    <n v="72000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <d v="2026-02-03T00:00:00"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="15"/>
+    <n v="2500"/>
+    <n v="37500"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <d v="2026-02-04T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="55000"/>
+    <n v="110000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <d v="2026-02-05T00:00:00"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="20"/>
+    <n v="800"/>
+    <n v="16000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <d v="2026-02-06T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="12000"/>
+    <n v="24000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <d v="2026-02-07T00:00:00"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="12"/>
+    <n v="1500"/>
+    <n v="18000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <d v="2026-02-08T00:00:00"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="3"/>
+    <n v="18000"/>
+    <n v="54000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <d v="2026-02-09T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="7"/>
+    <n v="2500"/>
+    <n v="17500"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <d v="2026-02-10T00:00:00"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="55000"/>
+    <n v="110000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <d v="2026-02-11T00:00:00"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="30"/>
+    <n v="800"/>
+    <n v="24000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <d v="2026-02-12T00:00:00"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="4"/>
+    <n v="12000"/>
+    <n v="48000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <d v="2026-02-13T00:00:00"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="15"/>
+    <n v="1500"/>
+    <n v="22500"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <d v="2026-02-14T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="18000"/>
+    <n v="36000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <d v="2026-02-15T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="10"/>
+    <n v="2500"/>
+    <n v="25000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <d v="2026-02-16T00:00:00"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="3"/>
+    <n v="55000"/>
+    <n v="165000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <d v="2026-02-17T00:00:00"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="22"/>
+    <n v="800"/>
+    <n v="17600"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <d v="2026-02-18T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <n v="5"/>
+    <n v="12000"/>
+    <n v="60000"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <d v="2026-02-19T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="11"/>
+    <n v="1500"/>
+    <n v="16500"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <d v="2026-02-20T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="18000"/>
+    <n v="36000"/>
+    <s v="Cash"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <d v="2026-02-21T00:00:00"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="9"/>
+    <n v="2500"/>
+    <n v="22500"/>
+    <s v="UPI"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <d v="2026-02-22T00:00:00"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <n v="2"/>
+    <n v="55000"/>
+    <n v="110000"/>
+    <s v="Card"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <d v="2026-02-23T00:00:00"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <n v="28"/>
+    <n v="800"/>
+    <n v="22400"/>
+    <s v="UPI"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3BC2403C-6E60-4ADA-ACD9-51E24D74A9E7}" name="PivotTable13" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A28:C34" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item x="2"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item h="1" x="2"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item x="3"/>
+        <item h="1" x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="3"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EE12F40-31E9-421B-83CC-D088DA187331}" name="PivotTable12" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A20:F26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E567135-876D-46B1-9E3A-AE92BE0C6BB3}" name="PivotTable11" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1">
+  <location ref="A11:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField dataField="1" showAll="0">
+      <items count="51">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B85BB1-05AD-486C-AF4F-5B546E47E11A}" name="PivotTable10" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5800,6 +8329,497 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E42D0720-D89C-49FE-A48B-A8BA7AD95A9A}">
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6328125" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="7" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="54" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="57"/>
+    </row>
+    <row r="2" spans="1:10" ht="15">
+      <c r="A2" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2" s="61">
+        <f>DATE(2026,9,25)</f>
+        <v>46290</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="52">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
+      <c r="A3" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>364</v>
+      </c>
+      <c r="D3" s="64">
+        <f>TIME(6,9,15)</f>
+        <v>0.25642361111111112</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>359</v>
+      </c>
+      <c r="F3" s="64">
+        <f>TIME(21,20,10)</f>
+        <v>0.88900462962962967</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>360</v>
+      </c>
+      <c r="H3" s="64"/>
+      <c r="I3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="61">
+        <f>DATE(2026,9,1)+TIME(1,45,34)</f>
+        <v>46266.073310185187</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
+    </row>
+    <row r="5" spans="1:10" ht="15">
+      <c r="A5" s="58" t="s">
+        <v>350</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>365</v>
+      </c>
+      <c r="D5" s="61">
+        <f ca="1">TODAY()</f>
+        <v>46291</v>
+      </c>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
+    </row>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="65" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>356</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>366</v>
+      </c>
+      <c r="D6" s="68">
+        <f ca="1">NOW()</f>
+        <v>46291.525760648146</v>
+      </c>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+    </row>
+    <row r="8" spans="1:10" ht="15">
+      <c r="A8" s="36" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" s="72">
+        <v>44996</v>
+      </c>
+      <c r="D10" t="e">
+        <f>DATEVALUE(C10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
+      <c r="A11" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="C11" s="71">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D11" t="e">
+        <f>TIMEVALUE(C11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" s="53">
+        <f>MIN(C11)</f>
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
+      <c r="A13" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="72">
+        <v>44996</v>
+      </c>
+      <c r="D13">
+        <f>DAY(C13)</f>
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <f>DAY(C13)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
+      <c r="B14" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14">
+        <f>MONTH(C13)</f>
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <f>MONTH(C13)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="B15" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="D15" s="37">
+        <f>YEAR(C13)</f>
+        <v>2023</v>
+      </c>
+      <c r="H15">
+        <f>YEAR(C13)</f>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
+      <c r="B16" s="36" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15">
+      <c r="B17" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17">
+        <f>WEEKNUM(C13,1)</f>
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <f>WEEKDAY(C10,2)</f>
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <f>WEEKDAY(C13,2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15">
+      <c r="B18" s="36" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15">
+      <c r="B19" s="36" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15">
+      <c r="B20" s="36" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="C22" s="78" t="s">
+        <v>554</v>
+      </c>
+      <c r="D22" s="78" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15">
+      <c r="A23" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="C23" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D23" s="79">
+        <v>46675</v>
+      </c>
+      <c r="E23">
+        <f>DATEDIF(C23,D23,"Y")</f>
+        <v>1</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="J23">
+        <f>DATEDIF(C23,D23,"d")</f>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15">
+      <c r="A24" s="36"/>
+      <c r="B24" s="37" t="s">
+        <v>383</v>
+      </c>
+      <c r="C24" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D24" s="79">
+        <v>46371</v>
+      </c>
+      <c r="E24">
+        <f>DATEDIF(C24,D24,"m")</f>
+        <v>2</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15">
+      <c r="A25" s="36"/>
+      <c r="B25" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="C25" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D25" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E25">
+        <f>DATEDIF(C25,D25,"d")</f>
+        <v>20</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15">
+      <c r="A26" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="C26" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D26" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E26">
+        <f>_xlfn.DAYS(D26,C26)</f>
+        <v>20</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15">
+      <c r="A27" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="C27" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D27" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E27">
+        <f>NETWORKDAYS(C27,D27)</f>
+        <v>15</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15">
+      <c r="A28" s="36"/>
+      <c r="B28" s="37" t="s">
+        <v>389</v>
+      </c>
+      <c r="C28" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D28" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E28">
+        <f>NETWORKDAYS.INTL(C28,D28,11)</f>
+        <v>18</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15">
+      <c r="A29" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="C29" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D29" s="79">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15">
+      <c r="A30" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="C30" s="79">
+        <v>46290</v>
+      </c>
+      <c r="D30" s="79">
+        <v>46310</v>
+      </c>
+      <c r="E30">
+        <f>YEARFRAC(C30,D30)</f>
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15">
+      <c r="A32" s="37" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15">
+      <c r="A33" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>403</v>
+      </c>
+      <c r="C33" s="52">
+        <v>46290</v>
+      </c>
+      <c r="D33" s="52">
+        <f>EDATE(C33,3)</f>
+        <v>46381</v>
+      </c>
+      <c r="E33" s="52">
+        <f>EDATE(D33,-3)</f>
+        <v>46290</v>
+      </c>
+      <c r="G33" s="52">
+        <f>EDATE(C33,5)</f>
+        <v>46443</v>
+      </c>
+      <c r="H33" s="52">
+        <f>EDATE(C33,-5)</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>402</v>
+      </c>
+      <c r="C34" s="52">
+        <f>EOMONTH(C33,3)</f>
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="B35" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35">
+        <f>WORKDAY(C33,5)</f>
+        <v>46297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F700E6B1-D1A5-4261-AFA3-01D0C2A0EAD0}">
   <dimension ref="A1:H50"/>
@@ -5807,7 +8827,7 @@
   <cols>
     <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15">
@@ -6293,12 +9313,12 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15">
+    <row r="33" spans="1:8" ht="15">
       <c r="A33" s="36" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15">
+    <row r="34" spans="1:8" ht="15">
       <c r="A34" s="37" t="s">
         <v>408</v>
       </c>
@@ -6311,7 +9331,7 @@
       <c r="D34" s="77"/>
       <c r="E34" s="77"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -6323,8 +9343,16 @@
         <f>LOOKUP(A35,B$17:H$17,B$23:H$23)</f>
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="D35">
+        <f>LOOKUP(A35,A$17:H$17,A$19:H$19)</f>
+        <v>19</v>
+      </c>
+      <c r="E35">
+        <f ca="1">LOOKUP(A35,17:17,A20:H20)</f>
+        <v>44577</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -6336,8 +9364,16 @@
         <f t="shared" ref="C36:C40" si="2">LOOKUP(A36,B$17:H$17,B$23:H$23)</f>
         <v>Cuddalore</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="15">
+      <c r="D36">
+        <f t="shared" ref="D36:D40" si="3">LOOKUP(A36,A$17:H$17,A$19:H$19)</f>
+        <v>23</v>
+      </c>
+      <c r="E36" t="e">
+        <f t="shared" ref="E36:E40" si="4">LOOKUP(A36,18:18,A21:H21)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15">
       <c r="A37" s="37" t="s">
         <v>25</v>
       </c>
@@ -6349,8 +9385,16 @@
         <f t="shared" si="2"/>
         <v>Neyveli</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="15">
+      <c r="D37">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="E37" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15">
       <c r="A38" s="37" t="s">
         <v>28</v>
       </c>
@@ -6362,8 +9406,16 @@
         <f t="shared" si="2"/>
         <v>Cuddalore</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="D38">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="E38" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -6375,8 +9427,16 @@
         <f t="shared" si="2"/>
         <v>Cuddalore</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="D39">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="E39" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -6388,13 +9448,21 @@
         <f t="shared" si="2"/>
         <v>Cuddalore</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="15">
+      <c r="D40">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="E40" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15">
       <c r="A42" s="37" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15">
+    <row r="43" spans="1:8" ht="15">
       <c r="A43" s="37" t="s">
         <v>257</v>
       </c>
@@ -6404,8 +9472,9 @@
       <c r="C43" s="37" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="E43" s="80"/>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -6417,8 +9486,24 @@
         <f>_xlfn.XLOOKUP(A44,B$17:H$17,B$23:H$23,"Not found",0,1)</f>
         <v>Panruti</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="E44">
+        <f>_xlfn.XLOOKUP(A44,A$17:H$17,A$19:H$19,"not found",0)</f>
+        <v>19</v>
+      </c>
+      <c r="F44" t="str">
+        <f>_xlfn.XLOOKUP(A44,rawdata!A$2:A$101,rawdata!G$2:G$101,"Not Found",0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="G44" t="str">
+        <f>_xlfn.XLOOKUP(A44,A$17:H$17,A$22:H$22,"Not found",0)</f>
+        <v>Beach Road</v>
+      </c>
+      <c r="H44" s="85">
+        <f>_xlfn.XLOOKUP(A44,rawdata!A$2:A$101,rawdata!E$2:E$101,"not found",0)</f>
+        <v>44613</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -6427,11 +9512,27 @@
         <v>Aditya</v>
       </c>
       <c r="C45" t="str">
-        <f t="shared" ref="C45:C50" si="3">_xlfn.XLOOKUP(A45,B$17:H$17,B$23:H$23,"Not found",0,1)</f>
+        <f t="shared" ref="C45:C50" si="5">_xlfn.XLOOKUP(A45,B$17:H$17,B$23:H$23,"Not found",0,1)</f>
         <v>Not found</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="15">
+      <c r="E45" t="str">
+        <f t="shared" ref="E45:E50" si="6">_xlfn.XLOOKUP(A45,A$17:H$17,A$19:H$19,"not found",0)</f>
+        <v>not found</v>
+      </c>
+      <c r="F45" t="str">
+        <f>_xlfn.XLOOKUP(A45,rawdata!A$2:A$101,rawdata!G$2:G$101,"Not Found",0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" ref="G45:G50" si="7">_xlfn.XLOOKUP(A45,A$17:H$17,A$22:H$22,"Not found",0)</f>
+        <v>Not found</v>
+      </c>
+      <c r="H45" s="85">
+        <f>_xlfn.XLOOKUP(A45,rawdata!A$2:A$101,rawdata!E$2:E$101,"not found",0)</f>
+        <v>44633</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15">
       <c r="A46" s="37" t="s">
         <v>25</v>
       </c>
@@ -6440,11 +9541,27 @@
         <v>Pranitn</v>
       </c>
       <c r="C46" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Neyveli</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="15">
+      <c r="E46">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="F46" t="str">
+        <f>_xlfn.XLOOKUP(A46,rawdata!A$2:A$101,rawdata!G$2:G$101,"Not Found",0)</f>
+        <v>Neyveli</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="7"/>
+        <v>Keeranathan</v>
+      </c>
+      <c r="H46" s="85">
+        <f>_xlfn.XLOOKUP(A46,rawdata!A$2:A$101,rawdata!E$2:E$101,"not found",0)</f>
+        <v>44629</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15">
       <c r="A47" s="37" t="s">
         <v>28</v>
       </c>
@@ -6453,11 +9570,27 @@
         <v>Madhavn</v>
       </c>
       <c r="C47" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Cuddalore</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="E47">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="F47" t="str">
+        <f>_xlfn.XLOOKUP(A47,rawdata!A$2:A$101,rawdata!G$2:G$101,"Not Found",0)</f>
+        <v>Cuddalore</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="7"/>
+        <v>Varakalpattu</v>
+      </c>
+      <c r="H47" s="85">
+        <f>_xlfn.XLOOKUP(A47,rawdata!A$2:A$101,rawdata!E$2:E$101,"not found",0)</f>
+        <v>44639</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -6466,11 +9599,27 @@
         <v>Arjun</v>
       </c>
       <c r="C48" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Not found</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="E48" t="str">
+        <f t="shared" si="6"/>
+        <v>not found</v>
+      </c>
+      <c r="F48" t="str">
+        <f>_xlfn.XLOOKUP(A48,rawdata!A$2:A$101,rawdata!G$2:G$101,"Not Found",0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="7"/>
+        <v>Not found</v>
+      </c>
+      <c r="H48" s="85">
+        <f>_xlfn.XLOOKUP(A48,rawdata!A$2:A$101,rawdata!E$2:E$101,"not found",0)</f>
+        <v>44669</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -6479,12 +9628,28 @@
         <v>Mokshn</v>
       </c>
       <c r="C49" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Not found</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="15">
-      <c r="A50" s="37" t="s">
+      <c r="E49" t="str">
+        <f t="shared" si="6"/>
+        <v>not found</v>
+      </c>
+      <c r="F49" t="str">
+        <f>_xlfn.XLOOKUP(A49,rawdata!A$2:A$101,rawdata!G$2:G$101,"Not Found",0)</f>
+        <v>Panruti</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="7"/>
+        <v>Not found</v>
+      </c>
+      <c r="H49" s="85">
+        <f>_xlfn.XLOOKUP(A49,rawdata!A$2:A$101,rawdata!E$2:E$101,"not found",0)</f>
+        <v>44702</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15">
+      <c r="A50" s="80" t="s">
         <v>420</v>
       </c>
       <c r="B50" t="str">
@@ -6492,12 +9657,36 @@
         <v>not found</v>
       </c>
       <c r="C50" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Not found</v>
       </c>
+      <c r="E50" t="str">
+        <f t="shared" si="6"/>
+        <v>not found</v>
+      </c>
+      <c r="F50" t="str">
+        <f>_xlfn.XLOOKUP(A50,rawdata!A$2:A$101,rawdata!G$2:G$101,"Not Found",0)</f>
+        <v>Not Found</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="7"/>
+        <v>Not found</v>
+      </c>
+      <c r="H50" s="85" t="str">
+        <f>_xlfn.XLOOKUP(A50,rawdata!A$2:A$101,rawdata!E$2:E$101,"not found",0)</f>
+        <v>not found</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A53:A56" xr:uid="{B61B4F96-7DD1-499D-BBD1-052B1D198142}">
+      <formula1>$A$53:$A$56</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43" xr:uid="{040C08F8-05CF-4065-93CE-BB3EF3F8D205}">
+      <formula1>$A$44:$A$50</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6776,1659 +9965,353 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7A24AF-A89D-4410-B0AB-A75E15E06DC3}">
-  <dimension ref="A1:J52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8DE489A-1136-41EF-AEF7-C9C6AC1A537D}">
+  <dimension ref="A2:F34"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="76" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="76" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="81" t="s">
+        <v>557</v>
+      </c>
+      <c r="B3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="82" t="s">
+        <v>482</v>
+      </c>
+      <c r="B4" s="83">
+        <v>606400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="82" t="s">
+        <v>470</v>
+      </c>
+      <c r="B5" s="83">
+        <v>571400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="82" t="s">
+        <v>476</v>
+      </c>
+      <c r="B6" s="83">
+        <v>487000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="82" t="s">
+        <v>487</v>
+      </c>
+      <c r="B7" s="83">
+        <v>461600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="82" t="s">
+        <v>558</v>
+      </c>
+      <c r="B8" s="83">
+        <v>2126400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="81" t="s">
         <v>460</v>
       </c>
-      <c r="D2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G2" t="s">
-        <v>464</v>
-      </c>
-      <c r="H2" t="s">
-        <v>465</v>
-      </c>
-      <c r="I2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B3" s="52">
-        <v>46027</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B9" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="76" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="81" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="82" t="s">
+        <v>492</v>
+      </c>
+      <c r="B12" s="83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="82" t="s">
+        <v>483</v>
+      </c>
+      <c r="B13" s="83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="82" t="s">
+        <v>471</v>
+      </c>
+      <c r="B14" s="83">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="82" t="s">
+        <v>488</v>
+      </c>
+      <c r="B15" s="83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="82" t="s">
+        <v>477</v>
+      </c>
+      <c r="B16" s="83">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="82" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="82" t="s">
+        <v>558</v>
+      </c>
+      <c r="B18" s="83">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="81" t="s">
+        <v>559</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="81" t="s">
+        <v>557</v>
+      </c>
+      <c r="B21" t="s">
+        <v>482</v>
+      </c>
+      <c r="C21" t="s">
+        <v>470</v>
+      </c>
+      <c r="D21" t="s">
+        <v>476</v>
+      </c>
+      <c r="E21" t="s">
+        <v>487</v>
+      </c>
+      <c r="F21" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="82" t="s">
         <v>469</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B22" s="83">
+        <v>187000</v>
+      </c>
+      <c r="C22" s="83">
+        <v>311000</v>
+      </c>
+      <c r="D22" s="83">
+        <v>206000</v>
+      </c>
+      <c r="E22" s="83">
+        <v>200000</v>
+      </c>
+      <c r="F22" s="83">
+        <v>904000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="82" t="s">
+        <v>486</v>
+      </c>
+      <c r="B23" s="83">
+        <v>37000</v>
+      </c>
+      <c r="C23" s="83">
+        <v>79900</v>
+      </c>
+      <c r="D23" s="83">
+        <v>17500</v>
+      </c>
+      <c r="E23" s="83">
+        <v>91100</v>
+      </c>
+      <c r="F23" s="83">
+        <v>225500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="82" t="s">
+        <v>481</v>
+      </c>
+      <c r="B24" s="83">
+        <v>282500</v>
+      </c>
+      <c r="C24" s="83">
+        <v>144000</v>
+      </c>
+      <c r="D24" s="83">
+        <v>170000</v>
+      </c>
+      <c r="E24" s="83">
+        <v>139000</v>
+      </c>
+      <c r="F24" s="83">
+        <v>735500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="82" t="s">
+        <v>475</v>
+      </c>
+      <c r="B25" s="83">
+        <v>99900</v>
+      </c>
+      <c r="C25" s="83">
+        <v>36500</v>
+      </c>
+      <c r="D25" s="83">
+        <v>93500</v>
+      </c>
+      <c r="E25" s="83">
+        <v>31500</v>
+      </c>
+      <c r="F25" s="83">
+        <v>261400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="82" t="s">
+        <v>558</v>
+      </c>
+      <c r="B26" s="83">
+        <v>606400</v>
+      </c>
+      <c r="C26" s="83">
+        <v>571400</v>
+      </c>
+      <c r="D26" s="83">
+        <v>487000</v>
+      </c>
+      <c r="E26" s="83">
+        <v>461600</v>
+      </c>
+      <c r="F26" s="83">
+        <v>2126400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="81" t="s">
+        <v>559</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="81" t="s">
+        <v>557</v>
+      </c>
+      <c r="B29" t="s">
+        <v>481</v>
+      </c>
+      <c r="C29" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="82" t="s">
         <v>470</v>
       </c>
-      <c r="E3" t="s">
-        <v>471</v>
-      </c>
-      <c r="F3" t="s">
-        <v>472</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>55000</v>
-      </c>
-      <c r="I3">
-        <v>110000</v>
-      </c>
-      <c r="J3" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>474</v>
-      </c>
-      <c r="B4" s="52">
-        <v>46028</v>
-      </c>
-      <c r="C4" t="s">
-        <v>475</v>
-      </c>
-      <c r="D4" t="s">
-        <v>476</v>
-      </c>
-      <c r="E4" t="s">
-        <v>477</v>
-      </c>
-      <c r="F4" t="s">
-        <v>478</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4">
-        <v>800</v>
-      </c>
-      <c r="I4">
-        <v>8000</v>
-      </c>
-      <c r="J4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B5" s="52">
-        <v>46029</v>
-      </c>
-      <c r="C5" t="s">
-        <v>481</v>
-      </c>
-      <c r="D5" t="s">
-        <v>482</v>
-      </c>
-      <c r="E5" t="s">
-        <v>483</v>
-      </c>
-      <c r="F5" t="s">
-        <v>478</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>1500</v>
-      </c>
-      <c r="I5">
-        <v>7500</v>
-      </c>
-      <c r="J5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>485</v>
-      </c>
-      <c r="B6" s="52">
-        <v>46030</v>
-      </c>
-      <c r="C6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="B30" s="83">
+        <v>144000</v>
+      </c>
+      <c r="C30" s="83">
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="84" t="s">
+        <v>490</v>
+      </c>
+      <c r="B31" s="83">
+        <v>144000</v>
+      </c>
+      <c r="C31" s="83">
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="82" t="s">
         <v>487</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B32" s="83">
+        <v>84000</v>
+      </c>
+      <c r="C32" s="83">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="84" t="s">
         <v>488</v>
       </c>
-      <c r="F6" t="s">
-        <v>472</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>12000</v>
-      </c>
-      <c r="I6">
-        <v>36000</v>
-      </c>
-      <c r="J6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>489</v>
-      </c>
-      <c r="B7" s="52">
-        <v>46031</v>
-      </c>
-      <c r="C7" t="s">
-        <v>469</v>
-      </c>
-      <c r="D7" t="s">
-        <v>476</v>
-      </c>
-      <c r="E7" t="s">
-        <v>490</v>
-      </c>
-      <c r="F7" t="s">
-        <v>472</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>18000</v>
-      </c>
-      <c r="I7">
-        <v>36000</v>
-      </c>
-      <c r="J7" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>491</v>
-      </c>
-      <c r="B8" s="52">
-        <v>46032</v>
-      </c>
-      <c r="C8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D8" t="s">
-        <v>470</v>
-      </c>
-      <c r="E8" t="s">
-        <v>492</v>
-      </c>
-      <c r="F8" t="s">
-        <v>478</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-      <c r="H8">
-        <v>2500</v>
-      </c>
-      <c r="I8">
-        <v>20000</v>
-      </c>
-      <c r="J8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>493</v>
-      </c>
-      <c r="B9" s="52">
-        <v>46033</v>
-      </c>
-      <c r="C9" t="s">
-        <v>481</v>
-      </c>
-      <c r="D9" t="s">
-        <v>487</v>
-      </c>
-      <c r="E9" t="s">
-        <v>471</v>
-      </c>
-      <c r="F9" t="s">
-        <v>472</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>55000</v>
-      </c>
-      <c r="I9">
-        <v>55000</v>
-      </c>
-      <c r="J9" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>494</v>
-      </c>
-      <c r="B10" s="52">
-        <v>46034</v>
-      </c>
-      <c r="C10" t="s">
-        <v>486</v>
-      </c>
-      <c r="D10" t="s">
-        <v>482</v>
-      </c>
-      <c r="E10" t="s">
-        <v>477</v>
-      </c>
-      <c r="F10" t="s">
-        <v>478</v>
-      </c>
-      <c r="G10">
-        <v>15</v>
-      </c>
-      <c r="H10">
-        <v>800</v>
-      </c>
-      <c r="I10">
-        <v>12000</v>
-      </c>
-      <c r="J10" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>495</v>
-      </c>
-      <c r="B11" s="52">
-        <v>46035</v>
-      </c>
-      <c r="C11" t="s">
-        <v>469</v>
-      </c>
-      <c r="D11" t="s">
-        <v>482</v>
-      </c>
-      <c r="E11" t="s">
-        <v>488</v>
-      </c>
-      <c r="F11" t="s">
-        <v>472</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>12000</v>
-      </c>
-      <c r="I11">
-        <v>48000</v>
-      </c>
-      <c r="J11" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>496</v>
-      </c>
-      <c r="B12" s="52">
-        <v>46036</v>
-      </c>
-      <c r="C12" t="s">
-        <v>475</v>
-      </c>
-      <c r="D12" t="s">
-        <v>476</v>
-      </c>
-      <c r="E12" t="s">
-        <v>483</v>
-      </c>
-      <c r="F12" t="s">
-        <v>478</v>
-      </c>
-      <c r="G12">
-        <v>7</v>
-      </c>
-      <c r="H12">
-        <v>1500</v>
-      </c>
-      <c r="I12">
-        <v>10500</v>
-      </c>
-      <c r="J12" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>497</v>
-      </c>
-      <c r="B13" s="52">
-        <v>46037</v>
-      </c>
-      <c r="C13" t="s">
-        <v>481</v>
-      </c>
-      <c r="D13" t="s">
-        <v>470</v>
-      </c>
-      <c r="E13" t="s">
-        <v>490</v>
-      </c>
-      <c r="F13" t="s">
-        <v>472</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13">
-        <v>18000</v>
-      </c>
-      <c r="I13">
-        <v>54000</v>
-      </c>
-      <c r="J13" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>498</v>
-      </c>
-      <c r="B14" s="52">
-        <v>46038</v>
-      </c>
-      <c r="C14" t="s">
-        <v>486</v>
-      </c>
-      <c r="D14" t="s">
-        <v>487</v>
-      </c>
-      <c r="E14" t="s">
-        <v>492</v>
-      </c>
-      <c r="F14" t="s">
-        <v>478</v>
-      </c>
-      <c r="G14">
-        <v>6</v>
-      </c>
-      <c r="H14">
-        <v>2500</v>
-      </c>
-      <c r="I14">
-        <v>15000</v>
-      </c>
-      <c r="J14" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>499</v>
-      </c>
-      <c r="B15" s="52">
-        <v>46039</v>
-      </c>
-      <c r="C15" t="s">
-        <v>469</v>
-      </c>
-      <c r="D15" t="s">
-        <v>470</v>
-      </c>
-      <c r="E15" t="s">
-        <v>471</v>
-      </c>
-      <c r="F15" t="s">
-        <v>472</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15">
-        <v>55000</v>
-      </c>
-      <c r="I15">
-        <v>165000</v>
-      </c>
-      <c r="J15" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>500</v>
-      </c>
-      <c r="B16" s="52">
-        <v>46040</v>
-      </c>
-      <c r="C16" t="s">
-        <v>475</v>
-      </c>
-      <c r="D16" t="s">
-        <v>482</v>
-      </c>
-      <c r="E16" t="s">
-        <v>477</v>
-      </c>
-      <c r="F16" t="s">
-        <v>478</v>
-      </c>
-      <c r="G16">
-        <v>20</v>
-      </c>
-      <c r="H16">
-        <v>800</v>
-      </c>
-      <c r="I16">
-        <v>16000</v>
-      </c>
-      <c r="J16" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>501</v>
-      </c>
-      <c r="B17" s="52">
-        <v>46041</v>
-      </c>
-      <c r="C17" t="s">
-        <v>481</v>
-      </c>
-      <c r="D17" t="s">
-        <v>476</v>
-      </c>
-      <c r="E17" t="s">
-        <v>488</v>
-      </c>
-      <c r="F17" t="s">
-        <v>472</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-      <c r="H17">
-        <v>12000</v>
-      </c>
-      <c r="I17">
-        <v>24000</v>
-      </c>
-      <c r="J17" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>502</v>
-      </c>
-      <c r="B18" s="52">
-        <v>46042</v>
-      </c>
-      <c r="C18" t="s">
-        <v>486</v>
-      </c>
-      <c r="D18" t="s">
-        <v>470</v>
-      </c>
-      <c r="E18" t="s">
-        <v>483</v>
-      </c>
-      <c r="F18" t="s">
-        <v>478</v>
-      </c>
-      <c r="G18">
-        <v>10</v>
-      </c>
-      <c r="H18">
-        <v>1500</v>
-      </c>
-      <c r="I18">
-        <v>15000</v>
-      </c>
-      <c r="J18" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>503</v>
-      </c>
-      <c r="B19" s="52">
-        <v>46043</v>
-      </c>
-      <c r="C19" t="s">
-        <v>469</v>
-      </c>
-      <c r="D19" t="s">
-        <v>487</v>
-      </c>
-      <c r="E19" t="s">
-        <v>490</v>
-      </c>
-      <c r="F19" t="s">
-        <v>472</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>18000</v>
-      </c>
-      <c r="I19">
-        <v>18000</v>
-      </c>
-      <c r="J19" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>504</v>
-      </c>
-      <c r="B20" s="52">
-        <v>46044</v>
-      </c>
-      <c r="C20" t="s">
-        <v>475</v>
-      </c>
-      <c r="D20" t="s">
-        <v>476</v>
-      </c>
-      <c r="E20" t="s">
-        <v>492</v>
-      </c>
-      <c r="F20" t="s">
-        <v>478</v>
-      </c>
-      <c r="G20">
-        <v>12</v>
-      </c>
-      <c r="H20">
-        <v>2500</v>
-      </c>
-      <c r="I20">
-        <v>30000</v>
-      </c>
-      <c r="J20" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>505</v>
-      </c>
-      <c r="B21" s="52">
-        <v>46045</v>
-      </c>
-      <c r="C21" t="s">
-        <v>481</v>
-      </c>
-      <c r="D21" t="s">
-        <v>482</v>
-      </c>
-      <c r="E21" t="s">
-        <v>471</v>
-      </c>
-      <c r="F21" t="s">
-        <v>472</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21">
-        <v>55000</v>
-      </c>
-      <c r="I21">
-        <v>110000</v>
-      </c>
-      <c r="J21" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>506</v>
-      </c>
-      <c r="B22" s="52">
-        <v>46046</v>
-      </c>
-      <c r="C22" t="s">
-        <v>486</v>
-      </c>
-      <c r="D22" t="s">
-        <v>470</v>
-      </c>
-      <c r="E22" t="s">
-        <v>477</v>
-      </c>
-      <c r="F22" t="s">
-        <v>478</v>
-      </c>
-      <c r="G22">
-        <v>18</v>
-      </c>
-      <c r="H22">
-        <v>800</v>
-      </c>
-      <c r="I22">
-        <v>14400</v>
-      </c>
-      <c r="J22" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>507</v>
-      </c>
-      <c r="B23" s="52">
-        <v>46047</v>
-      </c>
-      <c r="C23" t="s">
-        <v>469</v>
-      </c>
-      <c r="D23" t="s">
-        <v>476</v>
-      </c>
-      <c r="E23" t="s">
-        <v>488</v>
-      </c>
-      <c r="F23" t="s">
-        <v>472</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-      <c r="H23">
-        <v>12000</v>
-      </c>
-      <c r="I23">
-        <v>60000</v>
-      </c>
-      <c r="J23" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>508</v>
-      </c>
-      <c r="B24" s="52">
-        <v>46048</v>
-      </c>
-      <c r="C24" t="s">
-        <v>475</v>
-      </c>
-      <c r="D24" t="s">
-        <v>487</v>
-      </c>
-      <c r="E24" t="s">
-        <v>483</v>
-      </c>
-      <c r="F24" t="s">
-        <v>478</v>
-      </c>
-      <c r="G24">
-        <v>9</v>
-      </c>
-      <c r="H24">
-        <v>1500</v>
-      </c>
-      <c r="I24">
-        <v>13500</v>
-      </c>
-      <c r="J24" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>509</v>
-      </c>
-      <c r="B25" s="52">
-        <v>46049</v>
-      </c>
-      <c r="C25" t="s">
-        <v>481</v>
-      </c>
-      <c r="D25" t="s">
-        <v>470</v>
-      </c>
-      <c r="E25" t="s">
-        <v>490</v>
-      </c>
-      <c r="F25" t="s">
-        <v>472</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25">
-        <v>18000</v>
-      </c>
-      <c r="I25">
-        <v>36000</v>
-      </c>
-      <c r="J25" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>510</v>
-      </c>
-      <c r="B26" s="52">
-        <v>46050</v>
-      </c>
-      <c r="C26" t="s">
-        <v>486</v>
-      </c>
-      <c r="D26" t="s">
-        <v>482</v>
-      </c>
-      <c r="E26" t="s">
-        <v>492</v>
-      </c>
-      <c r="F26" t="s">
-        <v>478</v>
-      </c>
-      <c r="G26">
-        <v>10</v>
-      </c>
-      <c r="H26">
-        <v>2500</v>
-      </c>
-      <c r="I26">
-        <v>25000</v>
-      </c>
-      <c r="J26" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>511</v>
-      </c>
-      <c r="B27" s="52">
-        <v>46051</v>
-      </c>
-      <c r="C27" t="s">
-        <v>469</v>
-      </c>
-      <c r="D27" t="s">
-        <v>482</v>
-      </c>
-      <c r="E27" t="s">
-        <v>471</v>
-      </c>
-      <c r="F27" t="s">
-        <v>472</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>55000</v>
-      </c>
-      <c r="I27">
-        <v>55000</v>
-      </c>
-      <c r="J27" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>512</v>
-      </c>
-      <c r="B28" s="52">
-        <v>46052</v>
-      </c>
-      <c r="C28" t="s">
-        <v>475</v>
-      </c>
-      <c r="D28" t="s">
-        <v>476</v>
-      </c>
-      <c r="E28" t="s">
-        <v>477</v>
-      </c>
-      <c r="F28" t="s">
-        <v>478</v>
-      </c>
-      <c r="G28">
-        <v>25</v>
-      </c>
-      <c r="H28">
-        <v>800</v>
-      </c>
-      <c r="I28">
-        <v>20000</v>
-      </c>
-      <c r="J28" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>513</v>
-      </c>
-      <c r="B29" s="52">
-        <v>46053</v>
-      </c>
-      <c r="C29" t="s">
-        <v>481</v>
-      </c>
-      <c r="D29" t="s">
-        <v>487</v>
-      </c>
-      <c r="E29" t="s">
-        <v>488</v>
-      </c>
-      <c r="F29" t="s">
-        <v>472</v>
-      </c>
-      <c r="G29">
-        <v>3</v>
-      </c>
-      <c r="H29">
-        <v>12000</v>
-      </c>
-      <c r="I29">
-        <v>36000</v>
-      </c>
-      <c r="J29" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>514</v>
-      </c>
-      <c r="B30" s="52">
-        <v>46054</v>
-      </c>
-      <c r="C30" t="s">
-        <v>486</v>
-      </c>
-      <c r="D30" t="s">
-        <v>470</v>
-      </c>
-      <c r="E30" t="s">
-        <v>483</v>
-      </c>
-      <c r="F30" t="s">
-        <v>478</v>
-      </c>
-      <c r="G30">
-        <v>8</v>
-      </c>
-      <c r="H30">
-        <v>1500</v>
-      </c>
-      <c r="I30">
-        <v>12000</v>
-      </c>
-      <c r="J30" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>515</v>
-      </c>
-      <c r="B31" s="52">
-        <v>46055</v>
-      </c>
-      <c r="C31" t="s">
-        <v>469</v>
-      </c>
-      <c r="D31" t="s">
-        <v>487</v>
-      </c>
-      <c r="E31" t="s">
-        <v>490</v>
-      </c>
-      <c r="F31" t="s">
-        <v>472</v>
-      </c>
-      <c r="G31">
-        <v>4</v>
-      </c>
-      <c r="H31">
-        <v>18000</v>
-      </c>
-      <c r="I31">
-        <v>72000</v>
-      </c>
-      <c r="J31" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" t="s">
-        <v>516</v>
-      </c>
-      <c r="B32" s="52">
-        <v>46056</v>
-      </c>
-      <c r="C32" t="s">
-        <v>475</v>
-      </c>
-      <c r="D32" t="s">
-        <v>482</v>
-      </c>
-      <c r="E32" t="s">
-        <v>492</v>
-      </c>
-      <c r="F32" t="s">
-        <v>478</v>
-      </c>
-      <c r="G32">
-        <v>15</v>
-      </c>
-      <c r="H32">
-        <v>2500</v>
-      </c>
-      <c r="I32">
-        <v>37500</v>
-      </c>
-      <c r="J32" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>517</v>
-      </c>
-      <c r="B33" s="52">
-        <v>46057</v>
-      </c>
-      <c r="C33" t="s">
-        <v>481</v>
-      </c>
-      <c r="D33" t="s">
-        <v>476</v>
-      </c>
-      <c r="E33" t="s">
-        <v>471</v>
-      </c>
-      <c r="F33" t="s">
-        <v>472</v>
-      </c>
-      <c r="G33">
-        <v>2</v>
-      </c>
-      <c r="H33">
-        <v>55000</v>
-      </c>
-      <c r="I33">
-        <v>110000</v>
-      </c>
-      <c r="J33" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>518</v>
-      </c>
-      <c r="B34" s="52">
-        <v>46058</v>
-      </c>
-      <c r="C34" t="s">
-        <v>486</v>
-      </c>
-      <c r="D34" t="s">
-        <v>470</v>
-      </c>
-      <c r="E34" t="s">
-        <v>477</v>
-      </c>
-      <c r="F34" t="s">
-        <v>478</v>
-      </c>
-      <c r="G34">
-        <v>20</v>
-      </c>
-      <c r="H34">
-        <v>800</v>
-      </c>
-      <c r="I34">
-        <v>16000</v>
-      </c>
-      <c r="J34" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>519</v>
-      </c>
-      <c r="B35" s="52">
-        <v>46059</v>
-      </c>
-      <c r="C35" t="s">
-        <v>469</v>
-      </c>
-      <c r="D35" t="s">
-        <v>482</v>
-      </c>
-      <c r="E35" t="s">
-        <v>488</v>
-      </c>
-      <c r="F35" t="s">
-        <v>472</v>
-      </c>
-      <c r="G35">
-        <v>2</v>
-      </c>
-      <c r="H35">
-        <v>12000</v>
-      </c>
-      <c r="I35">
-        <v>24000</v>
-      </c>
-      <c r="J35" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>520</v>
-      </c>
-      <c r="B36" s="52">
-        <v>46060</v>
-      </c>
-      <c r="C36" t="s">
-        <v>475</v>
-      </c>
-      <c r="D36" t="s">
-        <v>487</v>
-      </c>
-      <c r="E36" t="s">
-        <v>483</v>
-      </c>
-      <c r="F36" t="s">
-        <v>478</v>
-      </c>
-      <c r="G36">
-        <v>12</v>
-      </c>
-      <c r="H36">
-        <v>1500</v>
-      </c>
-      <c r="I36">
-        <v>18000</v>
-      </c>
-      <c r="J36" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>521</v>
-      </c>
-      <c r="B37" s="52">
-        <v>46061</v>
-      </c>
-      <c r="C37" t="s">
-        <v>481</v>
-      </c>
-      <c r="D37" t="s">
-        <v>470</v>
-      </c>
-      <c r="E37" t="s">
-        <v>490</v>
-      </c>
-      <c r="F37" t="s">
-        <v>472</v>
-      </c>
-      <c r="G37">
-        <v>3</v>
-      </c>
-      <c r="H37">
-        <v>18000</v>
-      </c>
-      <c r="I37">
-        <v>54000</v>
-      </c>
-      <c r="J37" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" t="s">
-        <v>522</v>
-      </c>
-      <c r="B38" s="52">
-        <v>46062</v>
-      </c>
-      <c r="C38" t="s">
-        <v>486</v>
-      </c>
-      <c r="D38" t="s">
-        <v>476</v>
-      </c>
-      <c r="E38" t="s">
-        <v>492</v>
-      </c>
-      <c r="F38" t="s">
-        <v>478</v>
-      </c>
-      <c r="G38">
-        <v>7</v>
-      </c>
-      <c r="H38">
-        <v>2500</v>
-      </c>
-      <c r="I38">
-        <v>17500</v>
-      </c>
-      <c r="J38" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>523</v>
-      </c>
-      <c r="B39" s="52">
-        <v>46063</v>
-      </c>
-      <c r="C39" t="s">
-        <v>469</v>
-      </c>
-      <c r="D39" t="s">
-        <v>476</v>
-      </c>
-      <c r="E39" t="s">
-        <v>471</v>
-      </c>
-      <c r="F39" t="s">
-        <v>472</v>
-      </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-      <c r="H39">
-        <v>55000</v>
-      </c>
-      <c r="I39">
-        <v>110000</v>
-      </c>
-      <c r="J39" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>524</v>
-      </c>
-      <c r="B40" s="52">
-        <v>46064</v>
-      </c>
-      <c r="C40" t="s">
-        <v>475</v>
-      </c>
-      <c r="D40" t="s">
-        <v>482</v>
-      </c>
-      <c r="E40" t="s">
-        <v>477</v>
-      </c>
-      <c r="F40" t="s">
-        <v>478</v>
-      </c>
-      <c r="G40">
-        <v>30</v>
-      </c>
-      <c r="H40">
-        <v>800</v>
-      </c>
-      <c r="I40">
-        <v>24000</v>
-      </c>
-      <c r="J40" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" t="s">
-        <v>525</v>
-      </c>
-      <c r="B41" s="52">
-        <v>46065</v>
-      </c>
-      <c r="C41" t="s">
-        <v>481</v>
-      </c>
-      <c r="D41" t="s">
-        <v>487</v>
-      </c>
-      <c r="E41" t="s">
-        <v>488</v>
-      </c>
-      <c r="F41" t="s">
-        <v>472</v>
-      </c>
-      <c r="G41">
-        <v>4</v>
-      </c>
-      <c r="H41">
-        <v>12000</v>
-      </c>
-      <c r="I41">
-        <v>48000</v>
-      </c>
-      <c r="J41" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" t="s">
-        <v>526</v>
-      </c>
-      <c r="B42" s="52">
-        <v>46066</v>
-      </c>
-      <c r="C42" t="s">
-        <v>486</v>
-      </c>
-      <c r="D42" t="s">
-        <v>470</v>
-      </c>
-      <c r="E42" t="s">
-        <v>483</v>
-      </c>
-      <c r="F42" t="s">
-        <v>478</v>
-      </c>
-      <c r="G42">
-        <v>15</v>
-      </c>
-      <c r="H42">
-        <v>1500</v>
-      </c>
-      <c r="I42">
-        <v>22500</v>
-      </c>
-      <c r="J42" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" t="s">
-        <v>527</v>
-      </c>
-      <c r="B43" s="52">
-        <v>46067</v>
-      </c>
-      <c r="C43" t="s">
-        <v>469</v>
-      </c>
-      <c r="D43" t="s">
-        <v>470</v>
-      </c>
-      <c r="E43" t="s">
-        <v>490</v>
-      </c>
-      <c r="F43" t="s">
-        <v>472</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
-      <c r="H43">
-        <v>18000</v>
-      </c>
-      <c r="I43">
-        <v>36000</v>
-      </c>
-      <c r="J43" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" t="s">
-        <v>528</v>
-      </c>
-      <c r="B44" s="52">
-        <v>46068</v>
-      </c>
-      <c r="C44" t="s">
-        <v>475</v>
-      </c>
-      <c r="D44" t="s">
-        <v>476</v>
-      </c>
-      <c r="E44" t="s">
-        <v>492</v>
-      </c>
-      <c r="F44" t="s">
-        <v>478</v>
-      </c>
-      <c r="G44">
-        <v>10</v>
-      </c>
-      <c r="H44">
-        <v>2500</v>
-      </c>
-      <c r="I44">
-        <v>25000</v>
-      </c>
-      <c r="J44" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>529</v>
-      </c>
-      <c r="B45" s="52">
-        <v>46069</v>
-      </c>
-      <c r="C45" t="s">
-        <v>481</v>
-      </c>
-      <c r="D45" t="s">
-        <v>482</v>
-      </c>
-      <c r="E45" t="s">
-        <v>471</v>
-      </c>
-      <c r="F45" t="s">
-        <v>472</v>
-      </c>
-      <c r="G45">
-        <v>3</v>
-      </c>
-      <c r="H45">
-        <v>55000</v>
-      </c>
-      <c r="I45">
-        <v>165000</v>
-      </c>
-      <c r="J45" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" t="s">
-        <v>530</v>
-      </c>
-      <c r="B46" s="52">
-        <v>46070</v>
-      </c>
-      <c r="C46" t="s">
-        <v>486</v>
-      </c>
-      <c r="D46" t="s">
-        <v>487</v>
-      </c>
-      <c r="E46" t="s">
-        <v>477</v>
-      </c>
-      <c r="F46" t="s">
-        <v>478</v>
-      </c>
-      <c r="G46">
-        <v>22</v>
-      </c>
-      <c r="H46">
-        <v>800</v>
-      </c>
-      <c r="I46">
-        <v>17600</v>
-      </c>
-      <c r="J46" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" t="s">
-        <v>531</v>
-      </c>
-      <c r="B47" s="52">
-        <v>46071</v>
-      </c>
-      <c r="C47" t="s">
-        <v>469</v>
-      </c>
-      <c r="D47" t="s">
-        <v>482</v>
-      </c>
-      <c r="E47" t="s">
-        <v>488</v>
-      </c>
-      <c r="F47" t="s">
-        <v>472</v>
-      </c>
-      <c r="G47">
-        <v>5</v>
-      </c>
-      <c r="H47">
-        <v>12000</v>
-      </c>
-      <c r="I47">
-        <v>60000</v>
-      </c>
-      <c r="J47" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" t="s">
-        <v>532</v>
-      </c>
-      <c r="B48" s="52">
-        <v>46072</v>
-      </c>
-      <c r="C48" t="s">
-        <v>475</v>
-      </c>
-      <c r="D48" t="s">
-        <v>470</v>
-      </c>
-      <c r="E48" t="s">
-        <v>483</v>
-      </c>
-      <c r="F48" t="s">
-        <v>478</v>
-      </c>
-      <c r="G48">
-        <v>11</v>
-      </c>
-      <c r="H48">
-        <v>1500</v>
-      </c>
-      <c r="I48">
-        <v>16500</v>
-      </c>
-      <c r="J48" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" t="s">
-        <v>533</v>
-      </c>
-      <c r="B49" s="52">
-        <v>46073</v>
-      </c>
-      <c r="C49" t="s">
-        <v>481</v>
-      </c>
-      <c r="D49" t="s">
-        <v>476</v>
-      </c>
-      <c r="E49" t="s">
-        <v>490</v>
-      </c>
-      <c r="F49" t="s">
-        <v>472</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="H49">
-        <v>18000</v>
-      </c>
-      <c r="I49">
-        <v>36000</v>
-      </c>
-      <c r="J49" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>534</v>
-      </c>
-      <c r="B50" s="52">
-        <v>46074</v>
-      </c>
-      <c r="C50" t="s">
-        <v>486</v>
-      </c>
-      <c r="D50" t="s">
-        <v>487</v>
-      </c>
-      <c r="E50" t="s">
-        <v>492</v>
-      </c>
-      <c r="F50" t="s">
-        <v>478</v>
-      </c>
-      <c r="G50">
-        <v>9</v>
-      </c>
-      <c r="H50">
-        <v>2500</v>
-      </c>
-      <c r="I50">
-        <v>22500</v>
-      </c>
-      <c r="J50" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>535</v>
-      </c>
-      <c r="B51" s="52">
-        <v>46075</v>
-      </c>
-      <c r="C51" t="s">
-        <v>469</v>
-      </c>
-      <c r="D51" t="s">
-        <v>487</v>
-      </c>
-      <c r="E51" t="s">
-        <v>471</v>
-      </c>
-      <c r="F51" t="s">
-        <v>472</v>
-      </c>
-      <c r="G51">
-        <v>2</v>
-      </c>
-      <c r="H51">
-        <v>55000</v>
-      </c>
-      <c r="I51">
-        <v>110000</v>
-      </c>
-      <c r="J51" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" t="s">
-        <v>536</v>
-      </c>
-      <c r="B52" s="52">
-        <v>46076</v>
-      </c>
-      <c r="C52" t="s">
-        <v>475</v>
-      </c>
-      <c r="D52" t="s">
-        <v>482</v>
-      </c>
-      <c r="E52" t="s">
-        <v>477</v>
-      </c>
-      <c r="F52" t="s">
-        <v>478</v>
-      </c>
-      <c r="G52">
-        <v>28</v>
-      </c>
-      <c r="H52">
-        <v>800</v>
-      </c>
-      <c r="I52">
-        <v>22400</v>
-      </c>
-      <c r="J52" t="s">
-        <v>479</v>
+      <c r="B33" s="83">
+        <v>84000</v>
+      </c>
+      <c r="C33" s="83">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="82" t="s">
+        <v>558</v>
+      </c>
+      <c r="B34" s="83">
+        <v>228000</v>
+      </c>
+      <c r="C34" s="83">
+        <v>228000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -10123,11 +12006,91 @@
       </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M18:M20" xr:uid="{2CA19319-5AC8-4EC0-AF30-00153F56C291}">
+      <formula1>$J:$J</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64947FF0-2281-4C42-9658-9B8242D4095E}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="14.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5">
+        <v>545</v>
+      </c>
+      <c r="E5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="E6" t="s">
+        <v>566</v>
+      </c>
+      <c r="F6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="E7" t="s">
+        <v>567</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6" xr:uid="{42F4EFFE-4911-4F50-8D7E-8E2F56A29D92}">
+      <formula1>$A$1:$A$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
@@ -10207,7 +12170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3073DD66-6F87-4BE6-9313-9EA867561D3B}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -10230,7 +12193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FB00EB-1F40-48CD-BEDF-7ACFFA4D03F4}">
   <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -11220,495 +13183,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E42D0720-D89C-49FE-A48B-A8BA7AD95A9A}">
-  <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="2" max="2" width="46.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6328125" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" customWidth="1"/>
-    <col min="7" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15">
-      <c r="A1" s="54" t="s">
-        <v>346</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
-        <v>357</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>358</v>
-      </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="57"/>
-    </row>
-    <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="58" t="s">
-        <v>347</v>
-      </c>
-      <c r="B2" s="59" t="s">
-        <v>352</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>363</v>
-      </c>
-      <c r="D2" s="61">
-        <f>DATE(2026,9,25)</f>
-        <v>46290</v>
-      </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="52">
-        <v>45910</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15">
-      <c r="A3" s="58" t="s">
-        <v>348</v>
-      </c>
-      <c r="B3" s="59" t="s">
-        <v>353</v>
-      </c>
-      <c r="C3" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D3" s="64">
-        <f>TIME(6,9,15)</f>
-        <v>0.25642361111111112</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>359</v>
-      </c>
-      <c r="F3" s="64">
-        <f>TIME(21,20,10)</f>
-        <v>0.88900462962962967</v>
-      </c>
-      <c r="G3" s="60" t="s">
-        <v>360</v>
-      </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="63"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="58" t="s">
-        <v>349</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>354</v>
-      </c>
-      <c r="C4" s="60" t="s">
-        <v>361</v>
-      </c>
-      <c r="D4" s="61">
-        <f>DATE(2026,9,1)+TIME(1,45,34)</f>
-        <v>46266.073310185187</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>362</v>
-      </c>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="63"/>
-    </row>
-    <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="58" t="s">
-        <v>350</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>355</v>
-      </c>
-      <c r="C5" s="60" t="s">
-        <v>365</v>
-      </c>
-      <c r="D5" s="61">
-        <f ca="1">TODAY()</f>
-        <v>46290</v>
-      </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="63"/>
-    </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="65" t="s">
-        <v>351</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="67" t="s">
-        <v>366</v>
-      </c>
-      <c r="D6" s="68">
-        <f ca="1">NOW()</f>
-        <v>46290.525716203701</v>
-      </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-    </row>
-    <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="36" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="C10" s="72">
-        <v>44996</v>
-      </c>
-      <c r="D10" t="e">
-        <f>DATEVALUE(C10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15">
-      <c r="A11" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="C11" s="71">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="D11" t="e">
-        <f>TIMEVALUE(C11)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E11" s="53">
-        <f>MIN(C11)</f>
-        <v>0.72916666666666663</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="36" t="s">
-        <v>371</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>372</v>
-      </c>
-      <c r="C13" s="72">
-        <v>44996</v>
-      </c>
-      <c r="D13">
-        <f>DAY(C13)</f>
-        <v>11</v>
-      </c>
-      <c r="F13">
-        <f>DAY(C13)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15">
-      <c r="B14" s="36" t="s">
-        <v>373</v>
-      </c>
-      <c r="D14">
-        <f>MONTH(C13)</f>
-        <v>3</v>
-      </c>
-      <c r="F14">
-        <f>MONTH(C13)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15">
-      <c r="B15" s="36" t="s">
-        <v>374</v>
-      </c>
-      <c r="D15" s="37">
-        <f>YEAR(C13)</f>
-        <v>2023</v>
-      </c>
-      <c r="H15">
-        <f>YEAR(C13)</f>
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15">
-      <c r="B16" s="36" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15">
-      <c r="B17" s="36" t="s">
-        <v>376</v>
-      </c>
-      <c r="C17">
-        <f>WEEKNUM(C13,1)</f>
-        <v>10</v>
-      </c>
-      <c r="D17">
-        <f>WEEKDAY(C10,2)</f>
-        <v>6</v>
-      </c>
-      <c r="F17">
-        <f>WEEKDAY(C13,2)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15">
-      <c r="B18" s="36" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15">
-      <c r="B19" s="36" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15">
-      <c r="B20" s="36" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="36" t="s">
-        <v>380</v>
-      </c>
-      <c r="C22" s="78" t="s">
-        <v>554</v>
-      </c>
-      <c r="D22" s="78" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="36" t="s">
-        <v>381</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="C23" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D23" s="79">
-        <v>46675</v>
-      </c>
-      <c r="E23">
-        <f>DATEDIF(C23,D23,"Y")</f>
-        <v>1</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>394</v>
-      </c>
-      <c r="J23">
-        <f>DATEDIF(C23,D23,"d")</f>
-        <v>385</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="36"/>
-      <c r="B24" s="37" t="s">
-        <v>383</v>
-      </c>
-      <c r="C24" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D24" s="79">
-        <v>46371</v>
-      </c>
-      <c r="E24">
-        <f>DATEDIF(C24,D24,"m")</f>
-        <v>2</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15">
-      <c r="A25" s="36"/>
-      <c r="B25" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="C25" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D25" s="79">
-        <v>46310</v>
-      </c>
-      <c r="E25">
-        <f>DATEDIF(C25,D25,"d")</f>
-        <v>20</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15">
-      <c r="A26" s="36" t="s">
-        <v>385</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>386</v>
-      </c>
-      <c r="C26" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D26" s="79">
-        <v>46310</v>
-      </c>
-      <c r="E26">
-        <f>_xlfn.DAYS(D26,C26)</f>
-        <v>20</v>
-      </c>
-      <c r="F26" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="36" t="s">
-        <v>387</v>
-      </c>
-      <c r="B27" s="37" t="s">
-        <v>388</v>
-      </c>
-      <c r="C27" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D27" s="79">
-        <v>46310</v>
-      </c>
-      <c r="E27">
-        <f>NETWORKDAYS(C27,D27)</f>
-        <v>15</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="36"/>
-      <c r="B28" s="37" t="s">
-        <v>389</v>
-      </c>
-      <c r="C28" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D28" s="79">
-        <v>46310</v>
-      </c>
-      <c r="E28">
-        <f>NETWORKDAYS.INTL(C28,D28,11)</f>
-        <v>18</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15">
-      <c r="A29" s="36" t="s">
-        <v>390</v>
-      </c>
-      <c r="B29" s="37" t="s">
-        <v>392</v>
-      </c>
-      <c r="C29" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D29" s="79">
-        <v>46310</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="36" t="s">
-        <v>391</v>
-      </c>
-      <c r="B30" s="37" t="s">
-        <v>393</v>
-      </c>
-      <c r="C30" s="79">
-        <v>46290</v>
-      </c>
-      <c r="D30" s="79">
-        <v>46310</v>
-      </c>
-      <c r="E30">
-        <f>YEARFRAC(C30,D30)</f>
-        <v>5.5555555555555552E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="37" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="15">
-      <c r="A33" s="37" t="s">
-        <v>401</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>403</v>
-      </c>
-      <c r="C33" s="52">
-        <v>46290</v>
-      </c>
-      <c r="D33" s="52">
-        <f>EDATE(C33,3)</f>
-        <v>46381</v>
-      </c>
-      <c r="E33" s="52">
-        <f>EDATE(D33,-3)</f>
-        <v>46290</v>
-      </c>
-      <c r="G33" s="52">
-        <f>EDATE(C33,5)</f>
-        <v>46443</v>
-      </c>
-      <c r="H33" s="52">
-        <f>EDATE(C33,-5)</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15">
-      <c r="A34">
-        <v>0</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>402</v>
-      </c>
-      <c r="C34" s="52">
-        <f>EOMONTH(C33,3)</f>
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="B35" t="s">
-        <v>404</v>
-      </c>
-      <c r="C35">
-        <f>WORKDAY(C33,5)</f>
-        <v>46297</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>